--- a/Excel-files/ClosedSales1.xlsx
+++ b/Excel-files/ClosedSales1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="266">
   <si>
     <t>DateSelector</t>
   </si>
@@ -49,994 +49,769 @@
     <t>MSI</t>
   </si>
   <si>
-    <t>Land</t>
-  </si>
-  <si>
-    <t>558</t>
-  </si>
-  <si>
-    <t>Residential Income</t>
+    <t>FORT MYERS</t>
+  </si>
+  <si>
+    <t>474</t>
+  </si>
+  <si>
+    <t>FORT MYERS BEACH</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>BONITA SPRINGS</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>ESTERO</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>526</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>781</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>778</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>780</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>627</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>596</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>617</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>512</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>539</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>520</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>458</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>416</t>
+  </si>
+  <si>
+    <t>543</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>663</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>796</t>
+  </si>
+  <si>
+    <t>296</t>
+  </si>
+  <si>
+    <t>784</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>643</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>642</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>616</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>552</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>592</t>
   </si>
   <si>
     <t>40</t>
   </si>
   <si>
-    <t>Condominium</t>
-  </si>
-  <si>
-    <t>902</t>
-  </si>
-  <si>
-    <t>Single Family Residence</t>
-  </si>
-  <si>
-    <t>1272</t>
-  </si>
-  <si>
-    <t>588</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>1357</t>
-  </si>
-  <si>
-    <t>907</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>1898</t>
-  </si>
-  <si>
-    <t>696</t>
-  </si>
-  <si>
-    <t>1316</t>
-  </si>
-  <si>
-    <t>1350</t>
-  </si>
-  <si>
-    <t>670</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>1321</t>
+    <t>152</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>556</t>
+  </si>
+  <si>
+    <t>173</t>
   </si>
   <si>
     <t>679</t>
   </si>
   <si>
-    <t>2075</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>1854</t>
-  </si>
-  <si>
-    <t>1135</t>
-  </si>
-  <si>
-    <t>591</t>
+    <t>567</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>612</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>749</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>549</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>626</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>753</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>217</t>
   </si>
   <si>
     <t>66</t>
   </si>
   <si>
-    <t>656</t>
+    <t>133</t>
+  </si>
+  <si>
+    <t>681</t>
+  </si>
+  <si>
+    <t>717</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>779</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>756</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>889</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>653</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>720</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>1096</t>
+  </si>
+  <si>
+    <t>1052</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>298</t>
+  </si>
+  <si>
+    <t>849</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>955</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>810</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>714</t>
+  </si>
+  <si>
+    <t>722</t>
+  </si>
+  <si>
+    <t>659</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>675</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>748</t>
+  </si>
+  <si>
+    <t>553</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>108</t>
   </si>
   <si>
     <t>60</t>
   </si>
   <si>
-    <t>1640</t>
-  </si>
-  <si>
-    <t>915</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>968</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>485</t>
-  </si>
-  <si>
-    <t>1322</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>804</t>
-  </si>
-  <si>
-    <t>470</t>
+    <t>585</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>843</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>857</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>818</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>687</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>613</t>
+  </si>
+  <si>
+    <t>422</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>446</t>
+  </si>
+  <si>
+    <t>497</t>
   </si>
   <si>
     <t>55</t>
   </si>
   <si>
-    <t>777</t>
-  </si>
-  <si>
-    <t>1470</t>
-  </si>
-  <si>
-    <t>1389</t>
-  </si>
-  <si>
-    <t>481</t>
-  </si>
-  <si>
-    <t>815</t>
-  </si>
-  <si>
-    <t>774</t>
-  </si>
-  <si>
-    <t>1356</t>
-  </si>
-  <si>
-    <t>441</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>713</t>
-  </si>
-  <si>
-    <t>1117</t>
-  </si>
-  <si>
-    <t>464</t>
-  </si>
-  <si>
-    <t>832</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>535</t>
-  </si>
-  <si>
-    <t>1282</t>
-  </si>
-  <si>
-    <t>1867</t>
-  </si>
-  <si>
-    <t>660</t>
-  </si>
-  <si>
-    <t>1192</t>
-  </si>
-  <si>
-    <t>620</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>1520</t>
-  </si>
-  <si>
-    <t>2066</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>1407</t>
-  </si>
-  <si>
-    <t>2263</t>
-  </si>
-  <si>
-    <t>549</t>
-  </si>
-  <si>
-    <t>1844</t>
-  </si>
-  <si>
-    <t>498</t>
-  </si>
-  <si>
-    <t>1058</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>463</t>
-  </si>
-  <si>
-    <t>1016</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>1740</t>
-  </si>
-  <si>
-    <t>510</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>919</t>
+    <t>449</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>548</t>
+  </si>
+  <si>
+    <t>718</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>639</t>
+  </si>
+  <si>
+    <t>669</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>514</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>538</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>496</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>489</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>393</t>
+  </si>
+  <si>
+    <t>437</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>536</t>
+  </si>
+  <si>
+    <t>594</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>222</t>
+  </si>
+  <si>
+    <t>637</t>
+  </si>
+  <si>
+    <t>628</t>
+  </si>
+  <si>
+    <t>465</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>472</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>452</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>333</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>332</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>428</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>438</t>
+  </si>
+  <si>
+    <t>610</t>
+  </si>
+  <si>
+    <t>532</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>521</t>
+  </si>
+  <si>
+    <t>445</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>432</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>484</t>
+  </si>
+  <si>
+    <t>353</t>
   </si>
   <si>
     <t>479</t>
   </si>
   <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>1551</t>
-  </si>
-  <si>
-    <t>823</t>
-  </si>
-  <si>
-    <t>1590</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>898</t>
-  </si>
-  <si>
-    <t>513</t>
-  </si>
-  <si>
-    <t>1480</t>
-  </si>
-  <si>
-    <t>453</t>
-  </si>
-  <si>
-    <t>842</t>
-  </si>
-  <si>
-    <t>1126</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>1856</t>
-  </si>
-  <si>
-    <t>619</t>
-  </si>
-  <si>
-    <t>682</t>
-  </si>
-  <si>
-    <t>874</t>
-  </si>
-  <si>
-    <t>1381</t>
-  </si>
-  <si>
-    <t>1564</t>
-  </si>
-  <si>
-    <t>663</t>
-  </si>
-  <si>
-    <t>1056</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2175</t>
-  </si>
-  <si>
-    <t>714</t>
-  </si>
-  <si>
-    <t>1679</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>359</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>664</t>
-  </si>
-  <si>
-    <t>540</t>
-  </si>
-  <si>
-    <t>1339</t>
-  </si>
-  <si>
-    <t>1895</t>
-  </si>
-  <si>
-    <t>788</t>
-  </si>
-  <si>
-    <t>940</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>2325</t>
-  </si>
-  <si>
-    <t>1168</t>
-  </si>
-  <si>
-    <t>996</t>
-  </si>
-  <si>
-    <t>1145</t>
-  </si>
-  <si>
-    <t>2163</t>
-  </si>
-  <si>
-    <t>1190</t>
-  </si>
-  <si>
-    <t>1218</t>
-  </si>
-  <si>
-    <t>1229</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>2365</t>
-  </si>
-  <si>
-    <t>1466</t>
-  </si>
-  <si>
-    <t>1346</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>1035</t>
-  </si>
-  <si>
-    <t>2130</t>
-  </si>
-  <si>
-    <t>1341</t>
-  </si>
-  <si>
-    <t>1627</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>1127</t>
-  </si>
-  <si>
-    <t>2529</t>
-  </si>
-  <si>
-    <t>1155</t>
-  </si>
-  <si>
-    <t>1883</t>
-  </si>
-  <si>
-    <t>1309</t>
-  </si>
-  <si>
-    <t>1596</t>
-  </si>
-  <si>
-    <t>1617</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2139</t>
-  </si>
-  <si>
-    <t>2910</t>
-  </si>
-  <si>
-    <t>2356</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>2379</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>1979</t>
-  </si>
-  <si>
-    <t>2975</t>
-  </si>
-  <si>
-    <t>1625</t>
-  </si>
-  <si>
-    <t>2630</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>1613</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>2715</t>
-  </si>
-  <si>
-    <t>2251</t>
-  </si>
-  <si>
-    <t>1337</t>
-  </si>
-  <si>
-    <t>1369</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>1141</t>
-  </si>
-  <si>
-    <t>2032</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>1171</t>
-  </si>
-  <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>1136</t>
-  </si>
-  <si>
-    <t>2027</t>
-  </si>
-  <si>
-    <t>1028</t>
-  </si>
-  <si>
-    <t>1151</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>1957</t>
-  </si>
-  <si>
-    <t>1134</t>
-  </si>
-  <si>
-    <t>1987</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>1085</t>
-  </si>
-  <si>
-    <t>2124</t>
-  </si>
-  <si>
-    <t>1211</t>
-  </si>
-  <si>
-    <t>1304</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>1223</t>
-  </si>
-  <si>
-    <t>1634</t>
-  </si>
-  <si>
-    <t>978</t>
-  </si>
-  <si>
-    <t>1531</t>
-  </si>
-  <si>
-    <t>962</t>
-  </si>
-  <si>
-    <t>2449</t>
-  </si>
-  <si>
-    <t>1432</t>
-  </si>
-  <si>
-    <t>1887</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>1690</t>
-  </si>
-  <si>
-    <t>1536</t>
-  </si>
-  <si>
-    <t>2387</t>
-  </si>
-  <si>
-    <t>1513</t>
-  </si>
-  <si>
-    <t>1493</t>
-  </si>
-  <si>
-    <t>1210</t>
-  </si>
-  <si>
-    <t>1347</t>
-  </si>
-  <si>
-    <t>2094</t>
-  </si>
-  <si>
-    <t>1601</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>849</t>
-  </si>
-  <si>
-    <t>852</t>
-  </si>
-  <si>
-    <t>1656</t>
-  </si>
-  <si>
-    <t>785</t>
-  </si>
-  <si>
-    <t>839</t>
-  </si>
-  <si>
-    <t>640</t>
-  </si>
-  <si>
-    <t>1270</t>
-  </si>
-  <si>
-    <t>653</t>
-  </si>
-  <si>
-    <t>703</t>
-  </si>
-  <si>
-    <t>1140</t>
-  </si>
-  <si>
-    <t>1230</t>
-  </si>
-  <si>
-    <t>676</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>505</t>
-  </si>
-  <si>
-    <t>563</t>
-  </si>
-  <si>
-    <t>726</t>
-  </si>
-  <si>
-    <t>1446</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>644</t>
-  </si>
-  <si>
-    <t>1246</t>
-  </si>
-  <si>
-    <t>571</t>
-  </si>
-  <si>
-    <t>710</t>
-  </si>
-  <si>
-    <t>797</t>
-  </si>
-  <si>
-    <t>1568</t>
-  </si>
-  <si>
-    <t>1225</t>
-  </si>
-  <si>
-    <t>1014</t>
-  </si>
-  <si>
-    <t>2122</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>918</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>1055</t>
-  </si>
-  <si>
-    <t>1205</t>
-  </si>
-  <si>
-    <t>1919</t>
-  </si>
-  <si>
-    <t>933</t>
-  </si>
-  <si>
-    <t>955</t>
-  </si>
-  <si>
-    <t>883</t>
-  </si>
-  <si>
-    <t>1559</t>
-  </si>
-  <si>
-    <t>665</t>
-  </si>
-  <si>
-    <t>1024</t>
-  </si>
-  <si>
-    <t>1697</t>
-  </si>
-  <si>
-    <t>829</t>
-  </si>
-  <si>
-    <t>986</t>
-  </si>
-  <si>
-    <t>1500</t>
-  </si>
-  <si>
-    <t>939</t>
-  </si>
-  <si>
-    <t>668</t>
-  </si>
-  <si>
-    <t>1438</t>
-  </si>
-  <si>
-    <t>778</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>1269</t>
-  </si>
-  <si>
-    <t>628</t>
-  </si>
-  <si>
-    <t>764</t>
-  </si>
-  <si>
-    <t>746</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>596</t>
-  </si>
-  <si>
-    <t>826</t>
-  </si>
-  <si>
-    <t>803</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>1418</t>
-  </si>
-  <si>
-    <t>1027</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>2034</t>
-  </si>
-  <si>
-    <t>880</t>
-  </si>
-  <si>
-    <t>2068</t>
-  </si>
-  <si>
-    <t>2090</t>
-  </si>
-  <si>
-    <t>963</t>
-  </si>
-  <si>
-    <t>1725</t>
-  </si>
-  <si>
-    <t>765</t>
-  </si>
-  <si>
-    <t>712</t>
-  </si>
-  <si>
-    <t>1631</t>
-  </si>
-  <si>
-    <t>721</t>
-  </si>
-  <si>
-    <t>701</t>
-  </si>
-  <si>
-    <t>552</t>
-  </si>
-  <si>
-    <t>1344</t>
-  </si>
-  <si>
-    <t>622</t>
-  </si>
-  <si>
-    <t>526</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>625</t>
-  </si>
-  <si>
-    <t>1254</t>
-  </si>
-  <si>
-    <t>502</t>
-  </si>
-  <si>
-    <t>442</t>
-  </si>
-  <si>
-    <t>1197</t>
-  </si>
-  <si>
-    <t>1392</t>
-  </si>
-  <si>
-    <t>648</t>
-  </si>
-  <si>
-    <t>654</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
-    <t>567</t>
-  </si>
-  <si>
-    <t>565</t>
-  </si>
-  <si>
-    <t>1361</t>
-  </si>
-  <si>
-    <t>541</t>
-  </si>
-  <si>
-    <t>639</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>645</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>606</t>
-  </si>
-  <si>
-    <t>1052</t>
-  </si>
-  <si>
-    <t>1973</t>
-  </si>
-  <si>
-    <t>896</t>
-  </si>
-  <si>
-    <t>564</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>483</t>
-  </si>
-  <si>
-    <t>1664</t>
-  </si>
-  <si>
-    <t>641</t>
-  </si>
-  <si>
-    <t>1587</t>
-  </si>
-  <si>
-    <t>423</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>1535</t>
-  </si>
-  <si>
-    <t>417</t>
-  </si>
-  <si>
-    <t>627</t>
-  </si>
-  <si>
-    <t>672</t>
-  </si>
-  <si>
-    <t>404</t>
-  </si>
-  <si>
-    <t>1547</t>
-  </si>
-  <si>
-    <t>1323</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>408</t>
-  </si>
-  <si>
-    <t>421</t>
-  </si>
-  <si>
-    <t>818</t>
-  </si>
-  <si>
-    <t>1265</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>1546</t>
-  </si>
-  <si>
-    <t>905</t>
-  </si>
-  <si>
-    <t>437</t>
-  </si>
-  <si>
-    <t>2217</t>
-  </si>
-  <si>
-    <t>499</t>
-  </si>
-  <si>
-    <t>1300</t>
-  </si>
-  <si>
-    <t>2214</t>
-  </si>
-  <si>
-    <t>492</t>
+    <t>64</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>683</t>
   </si>
 </sst>
 </file>
@@ -1392,7 +1167,7 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="13.57421875" customWidth="1"/>
-    <col min="2" max="2" width="23.421875" customWidth="1"/>
+    <col min="2" max="2" width="19.28125" customWidth="1"/>
     <col min="3" max="4" width="14.57421875" customWidth="1"/>
     <col min="5" max="5" width="15.140625" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" customWidth="1"/>
@@ -1519,7 +1294,7 @@
         <v>43159</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -1538,7 +1313,7 @@
         <v>43159</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7"/>
       <c r="D7"/>
@@ -1557,7 +1332,7 @@
         <v>43159</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C8"/>
       <c r="D8"/>
@@ -1576,7 +1351,7 @@
         <v>43159</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9"/>
       <c r="D9"/>
@@ -1584,7 +1359,7 @@
       <c r="F9"/>
       <c r="G9"/>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1595,7 +1370,7 @@
         <v>43190</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10"/>
       <c r="D10"/>
@@ -1603,7 +1378,7 @@
       <c r="F10"/>
       <c r="G10"/>
       <c r="H10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1622,7 +1397,7 @@
       <c r="F11"/>
       <c r="G11"/>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1633,7 +1408,7 @@
         <v>43190</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12"/>
       <c r="D12"/>
@@ -1641,7 +1416,7 @@
       <c r="F12"/>
       <c r="G12"/>
       <c r="H12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -1652,7 +1427,7 @@
         <v>43190</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C13"/>
       <c r="D13"/>
@@ -1660,7 +1435,7 @@
       <c r="F13"/>
       <c r="G13"/>
       <c r="H13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -1679,7 +1454,7 @@
       <c r="F14"/>
       <c r="G14"/>
       <c r="H14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -1690,7 +1465,7 @@
         <v>43220</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C15"/>
       <c r="D15"/>
@@ -1698,7 +1473,7 @@
       <c r="F15"/>
       <c r="G15"/>
       <c r="H15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -1709,7 +1484,7 @@
         <v>43220</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16"/>
       <c r="D16"/>
@@ -1717,7 +1492,7 @@
       <c r="F16"/>
       <c r="G16"/>
       <c r="H16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -1728,7 +1503,7 @@
         <v>43220</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C17"/>
       <c r="D17"/>
@@ -1736,7 +1511,7 @@
       <c r="F17"/>
       <c r="G17"/>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -1747,7 +1522,7 @@
         <v>43251</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C18"/>
       <c r="D18"/>
@@ -1755,7 +1530,7 @@
       <c r="F18"/>
       <c r="G18"/>
       <c r="H18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -1766,7 +1541,7 @@
         <v>43251</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C19"/>
       <c r="D19"/>
@@ -1774,7 +1549,7 @@
       <c r="F19"/>
       <c r="G19"/>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -1785,7 +1560,7 @@
         <v>43251</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C20"/>
       <c r="D20"/>
@@ -1793,7 +1568,7 @@
       <c r="F20"/>
       <c r="G20"/>
       <c r="H20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -1812,7 +1587,7 @@
       <c r="F21"/>
       <c r="G21"/>
       <c r="H21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -1823,7 +1598,7 @@
         <v>43281</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C22"/>
       <c r="D22"/>
@@ -1831,7 +1606,7 @@
       <c r="F22"/>
       <c r="G22"/>
       <c r="H22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -1842,7 +1617,7 @@
         <v>43281</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C23"/>
       <c r="D23"/>
@@ -1850,7 +1625,7 @@
       <c r="F23"/>
       <c r="G23"/>
       <c r="H23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
@@ -1869,7 +1644,7 @@
       <c r="F24"/>
       <c r="G24"/>
       <c r="H24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
@@ -1880,7 +1655,7 @@
         <v>43281</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C25"/>
       <c r="D25"/>
@@ -1888,7 +1663,7 @@
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
@@ -1899,7 +1674,7 @@
         <v>43312</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C26"/>
       <c r="D26"/>
@@ -1907,7 +1682,7 @@
       <c r="F26"/>
       <c r="G26"/>
       <c r="H26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
@@ -1918,7 +1693,7 @@
         <v>43312</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C27"/>
       <c r="D27"/>
@@ -1926,7 +1701,7 @@
       <c r="F27"/>
       <c r="G27"/>
       <c r="H27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I27"/>
       <c r="J27"/>
@@ -1937,7 +1712,7 @@
         <v>43312</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C28"/>
       <c r="D28"/>
@@ -1945,7 +1720,7 @@
       <c r="F28"/>
       <c r="G28"/>
       <c r="H28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
@@ -1956,7 +1731,7 @@
         <v>43312</v>
       </c>
       <c r="B29" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C29"/>
       <c r="D29"/>
@@ -1964,7 +1739,7 @@
       <c r="F29"/>
       <c r="G29"/>
       <c r="H29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I29"/>
       <c r="J29"/>
@@ -1975,7 +1750,7 @@
         <v>43343</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C30"/>
       <c r="D30"/>
@@ -1983,7 +1758,7 @@
       <c r="F30"/>
       <c r="G30"/>
       <c r="H30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I30"/>
       <c r="J30"/>
@@ -1994,7 +1769,7 @@
         <v>43343</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C31"/>
       <c r="D31"/>
@@ -2002,7 +1777,7 @@
       <c r="F31"/>
       <c r="G31"/>
       <c r="H31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I31"/>
       <c r="J31"/>
@@ -2013,7 +1788,7 @@
         <v>43343</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C32"/>
       <c r="D32"/>
@@ -2021,7 +1796,7 @@
       <c r="F32"/>
       <c r="G32"/>
       <c r="H32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I32"/>
       <c r="J32"/>
@@ -2040,7 +1815,7 @@
       <c r="F33"/>
       <c r="G33"/>
       <c r="H33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I33"/>
       <c r="J33"/>
@@ -2051,7 +1826,7 @@
         <v>43373</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C34"/>
       <c r="D34"/>
@@ -2059,7 +1834,7 @@
       <c r="F34"/>
       <c r="G34"/>
       <c r="H34" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="I34"/>
       <c r="J34"/>
@@ -2078,7 +1853,7 @@
       <c r="F35"/>
       <c r="G35"/>
       <c r="H35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I35"/>
       <c r="J35"/>
@@ -2097,7 +1872,7 @@
       <c r="F36"/>
       <c r="G36"/>
       <c r="H36" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I36"/>
       <c r="J36"/>
@@ -2108,7 +1883,7 @@
         <v>43373</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C37"/>
       <c r="D37"/>
@@ -2116,7 +1891,7 @@
       <c r="F37"/>
       <c r="G37"/>
       <c r="H37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I37"/>
       <c r="J37"/>
@@ -2127,7 +1902,7 @@
         <v>43404</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C38"/>
       <c r="D38"/>
@@ -2135,7 +1910,7 @@
       <c r="F38"/>
       <c r="G38"/>
       <c r="H38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I38"/>
       <c r="J38"/>
@@ -2146,7 +1921,7 @@
         <v>43404</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C39"/>
       <c r="D39"/>
@@ -2154,7 +1929,7 @@
       <c r="F39"/>
       <c r="G39"/>
       <c r="H39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I39"/>
       <c r="J39"/>
@@ -2165,7 +1940,7 @@
         <v>43404</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C40"/>
       <c r="D40"/>
@@ -2173,7 +1948,7 @@
       <c r="F40"/>
       <c r="G40"/>
       <c r="H40" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I40"/>
       <c r="J40"/>
@@ -2184,7 +1959,7 @@
         <v>43404</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C41"/>
       <c r="D41"/>
@@ -2192,7 +1967,7 @@
       <c r="F41"/>
       <c r="G41"/>
       <c r="H41" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I41"/>
       <c r="J41"/>
@@ -2203,7 +1978,7 @@
         <v>43434</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C42"/>
       <c r="D42"/>
@@ -2211,7 +1986,7 @@
       <c r="F42"/>
       <c r="G42"/>
       <c r="H42" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I42"/>
       <c r="J42"/>
@@ -2222,7 +1997,7 @@
         <v>43434</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C43"/>
       <c r="D43"/>
@@ -2230,7 +2005,7 @@
       <c r="F43"/>
       <c r="G43"/>
       <c r="H43" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I43"/>
       <c r="J43"/>
@@ -2241,7 +2016,7 @@
         <v>43434</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C44"/>
       <c r="D44"/>
@@ -2249,7 +2024,7 @@
       <c r="F44"/>
       <c r="G44"/>
       <c r="H44" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I44"/>
       <c r="J44"/>
@@ -2260,7 +2035,7 @@
         <v>43434</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C45"/>
       <c r="D45"/>
@@ -2268,7 +2043,7 @@
       <c r="F45"/>
       <c r="G45"/>
       <c r="H45" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I45"/>
       <c r="J45"/>
@@ -2279,7 +2054,7 @@
         <v>43465</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C46"/>
       <c r="D46"/>
@@ -2287,7 +2062,7 @@
       <c r="F46"/>
       <c r="G46"/>
       <c r="H46" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I46"/>
       <c r="J46"/>
@@ -2298,7 +2073,7 @@
         <v>43465</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C47"/>
       <c r="D47"/>
@@ -2306,7 +2081,7 @@
       <c r="F47"/>
       <c r="G47"/>
       <c r="H47" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I47"/>
       <c r="J47"/>
@@ -2317,7 +2092,7 @@
         <v>43465</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C48"/>
       <c r="D48"/>
@@ -2325,7 +2100,7 @@
       <c r="F48"/>
       <c r="G48"/>
       <c r="H48" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I48"/>
       <c r="J48"/>
@@ -2336,7 +2111,7 @@
         <v>43465</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C49"/>
       <c r="D49"/>
@@ -2344,7 +2119,7 @@
       <c r="F49"/>
       <c r="G49"/>
       <c r="H49" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I49"/>
       <c r="J49"/>
@@ -2355,7 +2130,7 @@
         <v>43496</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C50"/>
       <c r="D50"/>
@@ -2363,7 +2138,7 @@
       <c r="F50"/>
       <c r="G50"/>
       <c r="H50" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I50"/>
       <c r="J50"/>
@@ -2382,7 +2157,7 @@
       <c r="F51"/>
       <c r="G51"/>
       <c r="H51" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I51"/>
       <c r="J51"/>
@@ -2393,7 +2168,7 @@
         <v>43496</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C52"/>
       <c r="D52"/>
@@ -2401,7 +2176,7 @@
       <c r="F52"/>
       <c r="G52"/>
       <c r="H52" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I52"/>
       <c r="J52"/>
@@ -2420,7 +2195,7 @@
       <c r="F53"/>
       <c r="G53"/>
       <c r="H53" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I53"/>
       <c r="J53"/>
@@ -2431,7 +2206,7 @@
         <v>43524</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C54"/>
       <c r="D54"/>
@@ -2439,7 +2214,7 @@
       <c r="F54"/>
       <c r="G54"/>
       <c r="H54" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I54"/>
       <c r="J54"/>
@@ -2450,7 +2225,7 @@
         <v>43524</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C55"/>
       <c r="D55"/>
@@ -2458,7 +2233,7 @@
       <c r="F55"/>
       <c r="G55"/>
       <c r="H55" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I55"/>
       <c r="J55"/>
@@ -2469,7 +2244,7 @@
         <v>43524</v>
       </c>
       <c r="B56" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C56"/>
       <c r="D56"/>
@@ -2477,7 +2252,7 @@
       <c r="F56"/>
       <c r="G56"/>
       <c r="H56" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I56"/>
       <c r="J56"/>
@@ -2488,7 +2263,7 @@
         <v>43524</v>
       </c>
       <c r="B57" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C57"/>
       <c r="D57"/>
@@ -2496,7 +2271,7 @@
       <c r="F57"/>
       <c r="G57"/>
       <c r="H57" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I57"/>
       <c r="J57"/>
@@ -2507,7 +2282,7 @@
         <v>43555</v>
       </c>
       <c r="B58" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C58"/>
       <c r="D58"/>
@@ -2515,7 +2290,7 @@
       <c r="F58"/>
       <c r="G58"/>
       <c r="H58" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I58"/>
       <c r="J58"/>
@@ -2526,7 +2301,7 @@
         <v>43555</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C59"/>
       <c r="D59"/>
@@ -2534,7 +2309,7 @@
       <c r="F59"/>
       <c r="G59"/>
       <c r="H59" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="I59"/>
       <c r="J59"/>
@@ -2545,7 +2320,7 @@
         <v>43555</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C60"/>
       <c r="D60"/>
@@ -2553,7 +2328,7 @@
       <c r="F60"/>
       <c r="G60"/>
       <c r="H60" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="I60"/>
       <c r="J60"/>
@@ -2564,7 +2339,7 @@
         <v>43555</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C61"/>
       <c r="D61"/>
@@ -2572,7 +2347,7 @@
       <c r="F61"/>
       <c r="G61"/>
       <c r="H61" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I61"/>
       <c r="J61"/>
@@ -2583,7 +2358,7 @@
         <v>43585</v>
       </c>
       <c r="B62" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C62"/>
       <c r="D62"/>
@@ -2591,7 +2366,7 @@
       <c r="F62"/>
       <c r="G62"/>
       <c r="H62" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="I62"/>
       <c r="J62"/>
@@ -2602,7 +2377,7 @@
         <v>43585</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C63"/>
       <c r="D63"/>
@@ -2610,7 +2385,7 @@
       <c r="F63"/>
       <c r="G63"/>
       <c r="H63" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I63"/>
       <c r="J63"/>
@@ -2621,7 +2396,7 @@
         <v>43585</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C64"/>
       <c r="D64"/>
@@ -2629,7 +2404,7 @@
       <c r="F64"/>
       <c r="G64"/>
       <c r="H64" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I64"/>
       <c r="J64"/>
@@ -2640,7 +2415,7 @@
         <v>43585</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C65"/>
       <c r="D65"/>
@@ -2648,7 +2423,7 @@
       <c r="F65"/>
       <c r="G65"/>
       <c r="H65" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I65"/>
       <c r="J65"/>
@@ -2659,7 +2434,7 @@
         <v>43616</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C66"/>
       <c r="D66"/>
@@ -2667,7 +2442,7 @@
       <c r="F66"/>
       <c r="G66"/>
       <c r="H66" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I66"/>
       <c r="J66"/>
@@ -2678,7 +2453,7 @@
         <v>43616</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C67"/>
       <c r="D67"/>
@@ -2686,7 +2461,7 @@
       <c r="F67"/>
       <c r="G67"/>
       <c r="H67" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="I67"/>
       <c r="J67"/>
@@ -2697,7 +2472,7 @@
         <v>43616</v>
       </c>
       <c r="B68" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C68"/>
       <c r="D68"/>
@@ -2705,7 +2480,7 @@
       <c r="F68"/>
       <c r="G68"/>
       <c r="H68" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I68"/>
       <c r="J68"/>
@@ -2716,7 +2491,7 @@
         <v>43616</v>
       </c>
       <c r="B69" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C69"/>
       <c r="D69"/>
@@ -2724,7 +2499,7 @@
       <c r="F69"/>
       <c r="G69"/>
       <c r="H69" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="I69"/>
       <c r="J69"/>
@@ -2735,7 +2510,7 @@
         <v>43646</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C70"/>
       <c r="D70"/>
@@ -2743,7 +2518,7 @@
       <c r="F70"/>
       <c r="G70"/>
       <c r="H70" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I70"/>
       <c r="J70"/>
@@ -2762,7 +2537,7 @@
       <c r="F71"/>
       <c r="G71"/>
       <c r="H71" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I71"/>
       <c r="J71"/>
@@ -2773,7 +2548,7 @@
         <v>43646</v>
       </c>
       <c r="B72" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C72"/>
       <c r="D72"/>
@@ -2781,7 +2556,7 @@
       <c r="F72"/>
       <c r="G72"/>
       <c r="H72" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="I72"/>
       <c r="J72"/>
@@ -2792,7 +2567,7 @@
         <v>43646</v>
       </c>
       <c r="B73" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C73"/>
       <c r="D73"/>
@@ -2800,7 +2575,7 @@
       <c r="F73"/>
       <c r="G73"/>
       <c r="H73" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I73"/>
       <c r="J73"/>
@@ -2811,7 +2586,7 @@
         <v>43677</v>
       </c>
       <c r="B74" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C74"/>
       <c r="D74"/>
@@ -2819,7 +2594,7 @@
       <c r="F74"/>
       <c r="G74"/>
       <c r="H74" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I74"/>
       <c r="J74"/>
@@ -2830,7 +2605,7 @@
         <v>43677</v>
       </c>
       <c r="B75" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C75"/>
       <c r="D75"/>
@@ -2838,7 +2613,7 @@
       <c r="F75"/>
       <c r="G75"/>
       <c r="H75" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="I75"/>
       <c r="J75"/>
@@ -2849,7 +2624,7 @@
         <v>43677</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C76"/>
       <c r="D76"/>
@@ -2857,7 +2632,7 @@
       <c r="F76"/>
       <c r="G76"/>
       <c r="H76" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I76"/>
       <c r="J76"/>
@@ -2868,7 +2643,7 @@
         <v>43677</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C77"/>
       <c r="D77"/>
@@ -2876,7 +2651,7 @@
       <c r="F77"/>
       <c r="G77"/>
       <c r="H77" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I77"/>
       <c r="J77"/>
@@ -2895,7 +2670,7 @@
       <c r="F78"/>
       <c r="G78"/>
       <c r="H78" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I78"/>
       <c r="J78"/>
@@ -2914,7 +2689,7 @@
       <c r="F79"/>
       <c r="G79"/>
       <c r="H79" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I79"/>
       <c r="J79"/>
@@ -2933,7 +2708,7 @@
       <c r="F80"/>
       <c r="G80"/>
       <c r="H80" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I80"/>
       <c r="J80"/>
@@ -2952,7 +2727,7 @@
       <c r="F81"/>
       <c r="G81"/>
       <c r="H81" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="I81"/>
       <c r="J81"/>
@@ -2963,7 +2738,7 @@
         <v>43738</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C82"/>
       <c r="D82"/>
@@ -2971,7 +2746,7 @@
       <c r="F82"/>
       <c r="G82"/>
       <c r="H82" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I82"/>
       <c r="J82"/>
@@ -2982,7 +2757,7 @@
         <v>43738</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C83"/>
       <c r="D83"/>
@@ -2990,7 +2765,7 @@
       <c r="F83"/>
       <c r="G83"/>
       <c r="H83" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I83"/>
       <c r="J83"/>
@@ -3001,7 +2776,7 @@
         <v>43738</v>
       </c>
       <c r="B84" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C84"/>
       <c r="D84"/>
@@ -3009,7 +2784,7 @@
       <c r="F84"/>
       <c r="G84"/>
       <c r="H84" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="I84"/>
       <c r="J84"/>
@@ -3028,7 +2803,7 @@
       <c r="F85"/>
       <c r="G85"/>
       <c r="H85" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="I85"/>
       <c r="J85"/>
@@ -3039,7 +2814,7 @@
         <v>43769</v>
       </c>
       <c r="B86" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C86"/>
       <c r="D86"/>
@@ -3047,7 +2822,7 @@
       <c r="F86"/>
       <c r="G86"/>
       <c r="H86" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I86"/>
       <c r="J86"/>
@@ -3058,7 +2833,7 @@
         <v>43769</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C87"/>
       <c r="D87"/>
@@ -3066,7 +2841,7 @@
       <c r="F87"/>
       <c r="G87"/>
       <c r="H87" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="I87"/>
       <c r="J87"/>
@@ -3077,7 +2852,7 @@
         <v>43769</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C88"/>
       <c r="D88"/>
@@ -3085,7 +2860,7 @@
       <c r="F88"/>
       <c r="G88"/>
       <c r="H88" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="I88"/>
       <c r="J88"/>
@@ -3096,7 +2871,7 @@
         <v>43769</v>
       </c>
       <c r="B89" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C89"/>
       <c r="D89"/>
@@ -3104,7 +2879,7 @@
       <c r="F89"/>
       <c r="G89"/>
       <c r="H89" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="I89"/>
       <c r="J89"/>
@@ -3115,7 +2890,7 @@
         <v>43799</v>
       </c>
       <c r="B90" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C90"/>
       <c r="D90"/>
@@ -3123,7 +2898,7 @@
       <c r="F90"/>
       <c r="G90"/>
       <c r="H90" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="I90"/>
       <c r="J90"/>
@@ -3134,7 +2909,7 @@
         <v>43799</v>
       </c>
       <c r="B91" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C91"/>
       <c r="D91"/>
@@ -3142,7 +2917,7 @@
       <c r="F91"/>
       <c r="G91"/>
       <c r="H91" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I91"/>
       <c r="J91"/>
@@ -3153,7 +2928,7 @@
         <v>43799</v>
       </c>
       <c r="B92" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C92"/>
       <c r="D92"/>
@@ -3161,7 +2936,7 @@
       <c r="F92"/>
       <c r="G92"/>
       <c r="H92" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I92"/>
       <c r="J92"/>
@@ -3172,7 +2947,7 @@
         <v>43799</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C93"/>
       <c r="D93"/>
@@ -3180,7 +2955,7 @@
       <c r="F93"/>
       <c r="G93"/>
       <c r="H93" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="I93"/>
       <c r="J93"/>
@@ -3191,7 +2966,7 @@
         <v>43830</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C94"/>
       <c r="D94"/>
@@ -3199,7 +2974,7 @@
       <c r="F94"/>
       <c r="G94"/>
       <c r="H94" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="I94"/>
       <c r="J94"/>
@@ -3210,7 +2985,7 @@
         <v>43830</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C95"/>
       <c r="D95"/>
@@ -3218,7 +2993,7 @@
       <c r="F95"/>
       <c r="G95"/>
       <c r="H95" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="I95"/>
       <c r="J95"/>
@@ -3237,7 +3012,7 @@
       <c r="F96"/>
       <c r="G96"/>
       <c r="H96" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="I96"/>
       <c r="J96"/>
@@ -3256,7 +3031,7 @@
       <c r="F97"/>
       <c r="G97"/>
       <c r="H97" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="I97"/>
       <c r="J97"/>
@@ -3267,7 +3042,7 @@
         <v>43861</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C98"/>
       <c r="D98"/>
@@ -3275,7 +3050,7 @@
       <c r="F98"/>
       <c r="G98"/>
       <c r="H98" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I98"/>
       <c r="J98"/>
@@ -3286,7 +3061,7 @@
         <v>43861</v>
       </c>
       <c r="B99" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C99"/>
       <c r="D99"/>
@@ -3294,7 +3069,7 @@
       <c r="F99"/>
       <c r="G99"/>
       <c r="H99" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="I99"/>
       <c r="J99"/>
@@ -3313,7 +3088,7 @@
       <c r="F100"/>
       <c r="G100"/>
       <c r="H100" t="s">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="I100"/>
       <c r="J100"/>
@@ -3324,7 +3099,7 @@
         <v>43861</v>
       </c>
       <c r="B101" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C101"/>
       <c r="D101"/>
@@ -3332,7 +3107,7 @@
       <c r="F101"/>
       <c r="G101"/>
       <c r="H101" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="I101"/>
       <c r="J101"/>
@@ -3343,7 +3118,7 @@
         <v>43890</v>
       </c>
       <c r="B102" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C102"/>
       <c r="D102"/>
@@ -3351,7 +3126,7 @@
       <c r="F102"/>
       <c r="G102"/>
       <c r="H102" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="I102"/>
       <c r="J102"/>
@@ -3362,7 +3137,7 @@
         <v>43890</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C103"/>
       <c r="D103"/>
@@ -3370,7 +3145,7 @@
       <c r="F103"/>
       <c r="G103"/>
       <c r="H103" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="I103"/>
       <c r="J103"/>
@@ -3381,7 +3156,7 @@
         <v>43890</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C104"/>
       <c r="D104"/>
@@ -3389,7 +3164,7 @@
       <c r="F104"/>
       <c r="G104"/>
       <c r="H104" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="I104"/>
       <c r="J104"/>
@@ -3400,7 +3175,7 @@
         <v>43890</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C105"/>
       <c r="D105"/>
@@ -3408,7 +3183,7 @@
       <c r="F105"/>
       <c r="G105"/>
       <c r="H105" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I105"/>
       <c r="J105"/>
@@ -3427,7 +3202,7 @@
       <c r="F106"/>
       <c r="G106"/>
       <c r="H106" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="I106"/>
       <c r="J106"/>
@@ -3438,7 +3213,7 @@
         <v>43921</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C107"/>
       <c r="D107"/>
@@ -3446,7 +3221,7 @@
       <c r="F107"/>
       <c r="G107"/>
       <c r="H107" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="I107"/>
       <c r="J107"/>
@@ -3457,7 +3232,7 @@
         <v>43921</v>
       </c>
       <c r="B108" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C108"/>
       <c r="D108"/>
@@ -3465,7 +3240,7 @@
       <c r="F108"/>
       <c r="G108"/>
       <c r="H108" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="I108"/>
       <c r="J108"/>
@@ -3476,7 +3251,7 @@
         <v>43921</v>
       </c>
       <c r="B109" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C109"/>
       <c r="D109"/>
@@ -3484,7 +3259,7 @@
       <c r="F109"/>
       <c r="G109"/>
       <c r="H109" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="I109"/>
       <c r="J109"/>
@@ -3495,7 +3270,7 @@
         <v>43951</v>
       </c>
       <c r="B110" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C110"/>
       <c r="D110"/>
@@ -3503,7 +3278,7 @@
       <c r="F110"/>
       <c r="G110"/>
       <c r="H110" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="I110"/>
       <c r="J110"/>
@@ -3522,7 +3297,7 @@
       <c r="F111"/>
       <c r="G111"/>
       <c r="H111" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="I111"/>
       <c r="J111"/>
@@ -3541,7 +3316,7 @@
       <c r="F112"/>
       <c r="G112"/>
       <c r="H112" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="I112"/>
       <c r="J112"/>
@@ -3552,7 +3327,7 @@
         <v>43951</v>
       </c>
       <c r="B113" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C113"/>
       <c r="D113"/>
@@ -3560,7 +3335,7 @@
       <c r="F113"/>
       <c r="G113"/>
       <c r="H113" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="I113"/>
       <c r="J113"/>
@@ -3571,7 +3346,7 @@
         <v>43982</v>
       </c>
       <c r="B114" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C114"/>
       <c r="D114"/>
@@ -3579,7 +3354,7 @@
       <c r="F114"/>
       <c r="G114"/>
       <c r="H114" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="I114"/>
       <c r="J114"/>
@@ -3598,7 +3373,7 @@
       <c r="F115"/>
       <c r="G115"/>
       <c r="H115" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="I115"/>
       <c r="J115"/>
@@ -3617,7 +3392,7 @@
       <c r="F116"/>
       <c r="G116"/>
       <c r="H116" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="I116"/>
       <c r="J116"/>
@@ -3628,7 +3403,7 @@
         <v>43982</v>
       </c>
       <c r="B117" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C117"/>
       <c r="D117"/>
@@ -3636,7 +3411,7 @@
       <c r="F117"/>
       <c r="G117"/>
       <c r="H117" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="I117"/>
       <c r="J117"/>
@@ -3647,7 +3422,7 @@
         <v>44012</v>
       </c>
       <c r="B118" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C118"/>
       <c r="D118"/>
@@ -3655,7 +3430,7 @@
       <c r="F118"/>
       <c r="G118"/>
       <c r="H118" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="I118"/>
       <c r="J118"/>
@@ -3666,7 +3441,7 @@
         <v>44012</v>
       </c>
       <c r="B119" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C119"/>
       <c r="D119"/>
@@ -3674,7 +3449,7 @@
       <c r="F119"/>
       <c r="G119"/>
       <c r="H119" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="I119"/>
       <c r="J119"/>
@@ -3685,7 +3460,7 @@
         <v>44012</v>
       </c>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C120"/>
       <c r="D120"/>
@@ -3693,7 +3468,7 @@
       <c r="F120"/>
       <c r="G120"/>
       <c r="H120" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="I120"/>
       <c r="J120"/>
@@ -3712,7 +3487,7 @@
       <c r="F121"/>
       <c r="G121"/>
       <c r="H121" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="I121"/>
       <c r="J121"/>
@@ -3723,7 +3498,7 @@
         <v>44043</v>
       </c>
       <c r="B122" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C122"/>
       <c r="D122"/>
@@ -3731,7 +3506,7 @@
       <c r="F122"/>
       <c r="G122"/>
       <c r="H122" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="I122"/>
       <c r="J122"/>
@@ -3742,7 +3517,7 @@
         <v>44043</v>
       </c>
       <c r="B123" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C123"/>
       <c r="D123"/>
@@ -3750,7 +3525,7 @@
       <c r="F123"/>
       <c r="G123"/>
       <c r="H123" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I123"/>
       <c r="J123"/>
@@ -3761,7 +3536,7 @@
         <v>44043</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C124"/>
       <c r="D124"/>
@@ -3769,7 +3544,7 @@
       <c r="F124"/>
       <c r="G124"/>
       <c r="H124" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="I124"/>
       <c r="J124"/>
@@ -3780,7 +3555,7 @@
         <v>44043</v>
       </c>
       <c r="B125" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C125"/>
       <c r="D125"/>
@@ -3788,7 +3563,7 @@
       <c r="F125"/>
       <c r="G125"/>
       <c r="H125" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="I125"/>
       <c r="J125"/>
@@ -3799,7 +3574,7 @@
         <v>44074</v>
       </c>
       <c r="B126" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C126"/>
       <c r="D126"/>
@@ -3807,7 +3582,7 @@
       <c r="F126"/>
       <c r="G126"/>
       <c r="H126" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="I126"/>
       <c r="J126"/>
@@ -3818,7 +3593,7 @@
         <v>44074</v>
       </c>
       <c r="B127" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C127"/>
       <c r="D127"/>
@@ -3826,7 +3601,7 @@
       <c r="F127"/>
       <c r="G127"/>
       <c r="H127" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="I127"/>
       <c r="J127"/>
@@ -3845,7 +3620,7 @@
       <c r="F128"/>
       <c r="G128"/>
       <c r="H128" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="I128"/>
       <c r="J128"/>
@@ -3856,7 +3631,7 @@
         <v>44074</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C129"/>
       <c r="D129"/>
@@ -3864,7 +3639,7 @@
       <c r="F129"/>
       <c r="G129"/>
       <c r="H129" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="I129"/>
       <c r="J129"/>
@@ -3883,7 +3658,7 @@
       <c r="F130"/>
       <c r="G130"/>
       <c r="H130" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="I130"/>
       <c r="J130"/>
@@ -3902,7 +3677,7 @@
       <c r="F131"/>
       <c r="G131"/>
       <c r="H131" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="I131"/>
       <c r="J131"/>
@@ -3921,7 +3696,7 @@
       <c r="F132"/>
       <c r="G132"/>
       <c r="H132" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="I132"/>
       <c r="J132"/>
@@ -3940,7 +3715,7 @@
       <c r="F133"/>
       <c r="G133"/>
       <c r="H133" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="I133"/>
       <c r="J133"/>
@@ -3959,7 +3734,7 @@
       <c r="F134"/>
       <c r="G134"/>
       <c r="H134" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="I134"/>
       <c r="J134"/>
@@ -3970,7 +3745,7 @@
         <v>44135</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C135"/>
       <c r="D135"/>
@@ -3978,7 +3753,7 @@
       <c r="F135"/>
       <c r="G135"/>
       <c r="H135" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="I135"/>
       <c r="J135"/>
@@ -3989,7 +3764,7 @@
         <v>44135</v>
       </c>
       <c r="B136" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C136"/>
       <c r="D136"/>
@@ -3997,7 +3772,7 @@
       <c r="F136"/>
       <c r="G136"/>
       <c r="H136" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="I136"/>
       <c r="J136"/>
@@ -4016,7 +3791,7 @@
       <c r="F137"/>
       <c r="G137"/>
       <c r="H137" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="I137"/>
       <c r="J137"/>
@@ -4027,7 +3802,7 @@
         <v>44165</v>
       </c>
       <c r="B138" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C138"/>
       <c r="D138"/>
@@ -4035,7 +3810,7 @@
       <c r="F138"/>
       <c r="G138"/>
       <c r="H138" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="I138"/>
       <c r="J138"/>
@@ -4046,7 +3821,7 @@
         <v>44165</v>
       </c>
       <c r="B139" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C139"/>
       <c r="D139"/>
@@ -4054,7 +3829,7 @@
       <c r="F139"/>
       <c r="G139"/>
       <c r="H139" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="I139"/>
       <c r="J139"/>
@@ -4073,7 +3848,7 @@
       <c r="F140"/>
       <c r="G140"/>
       <c r="H140" t="s">
-        <v>142</v>
+        <v>23</v>
       </c>
       <c r="I140"/>
       <c r="J140"/>
@@ -4084,7 +3859,7 @@
         <v>44165</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C141"/>
       <c r="D141"/>
@@ -4092,7 +3867,7 @@
       <c r="F141"/>
       <c r="G141"/>
       <c r="H141" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="I141"/>
       <c r="J141"/>
@@ -4103,7 +3878,7 @@
         <v>44196</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C142"/>
       <c r="D142"/>
@@ -4111,7 +3886,7 @@
       <c r="F142"/>
       <c r="G142"/>
       <c r="H142" t="s">
-        <v>144</v>
+        <v>27</v>
       </c>
       <c r="I142"/>
       <c r="J142"/>
@@ -4122,7 +3897,7 @@
         <v>44196</v>
       </c>
       <c r="B143" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C143"/>
       <c r="D143"/>
@@ -4130,7 +3905,7 @@
       <c r="F143"/>
       <c r="G143"/>
       <c r="H143" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="I143"/>
       <c r="J143"/>
@@ -4149,7 +3924,7 @@
       <c r="F144"/>
       <c r="G144"/>
       <c r="H144" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="I144"/>
       <c r="J144"/>
@@ -4160,7 +3935,7 @@
         <v>44196</v>
       </c>
       <c r="B145" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C145"/>
       <c r="D145"/>
@@ -4168,7 +3943,7 @@
       <c r="F145"/>
       <c r="G145"/>
       <c r="H145" t="s">
-        <v>147</v>
+        <v>24</v>
       </c>
       <c r="I145"/>
       <c r="J145"/>
@@ -4179,7 +3954,7 @@
         <v>44227</v>
       </c>
       <c r="B146" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C146"/>
       <c r="D146"/>
@@ -4187,7 +3962,7 @@
       <c r="F146"/>
       <c r="G146"/>
       <c r="H146" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="I146"/>
       <c r="J146"/>
@@ -4198,7 +3973,7 @@
         <v>44227</v>
       </c>
       <c r="B147" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C147"/>
       <c r="D147"/>
@@ -4206,7 +3981,7 @@
       <c r="F147"/>
       <c r="G147"/>
       <c r="H147" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="I147"/>
       <c r="J147"/>
@@ -4217,7 +3992,7 @@
         <v>44227</v>
       </c>
       <c r="B148" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C148"/>
       <c r="D148"/>
@@ -4225,7 +4000,7 @@
       <c r="F148"/>
       <c r="G148"/>
       <c r="H148" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="I148"/>
       <c r="J148"/>
@@ -4236,7 +4011,7 @@
         <v>44227</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C149"/>
       <c r="D149"/>
@@ -4244,7 +4019,7 @@
       <c r="F149"/>
       <c r="G149"/>
       <c r="H149" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="I149"/>
       <c r="J149"/>
@@ -4263,7 +4038,7 @@
       <c r="F150"/>
       <c r="G150"/>
       <c r="H150" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="I150"/>
       <c r="J150"/>
@@ -4274,7 +4049,7 @@
         <v>44255</v>
       </c>
       <c r="B151" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C151"/>
       <c r="D151"/>
@@ -4282,7 +4057,7 @@
       <c r="F151"/>
       <c r="G151"/>
       <c r="H151" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="I151"/>
       <c r="J151"/>
@@ -4293,7 +4068,7 @@
         <v>44255</v>
       </c>
       <c r="B152" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C152"/>
       <c r="D152"/>
@@ -4301,7 +4076,7 @@
       <c r="F152"/>
       <c r="G152"/>
       <c r="H152" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="I152"/>
       <c r="J152"/>
@@ -4312,7 +4087,7 @@
         <v>44255</v>
       </c>
       <c r="B153" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C153"/>
       <c r="D153"/>
@@ -4320,7 +4095,7 @@
       <c r="F153"/>
       <c r="G153"/>
       <c r="H153" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="I153"/>
       <c r="J153"/>
@@ -4331,7 +4106,7 @@
         <v>44286</v>
       </c>
       <c r="B154" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C154"/>
       <c r="D154"/>
@@ -4339,7 +4114,7 @@
       <c r="F154"/>
       <c r="G154"/>
       <c r="H154" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="I154"/>
       <c r="J154"/>
@@ -4358,7 +4133,7 @@
       <c r="F155"/>
       <c r="G155"/>
       <c r="H155" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="I155"/>
       <c r="J155"/>
@@ -4377,7 +4152,7 @@
       <c r="F156"/>
       <c r="G156"/>
       <c r="H156" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="I156"/>
       <c r="J156"/>
@@ -4388,7 +4163,7 @@
         <v>44286</v>
       </c>
       <c r="B157" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C157"/>
       <c r="D157"/>
@@ -4396,7 +4171,7 @@
       <c r="F157"/>
       <c r="G157"/>
       <c r="H157" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="I157"/>
       <c r="J157"/>
@@ -4407,7 +4182,7 @@
         <v>44316</v>
       </c>
       <c r="B158" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C158"/>
       <c r="D158"/>
@@ -4415,7 +4190,7 @@
       <c r="F158"/>
       <c r="G158"/>
       <c r="H158" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="I158"/>
       <c r="J158"/>
@@ -4434,7 +4209,7 @@
       <c r="F159"/>
       <c r="G159"/>
       <c r="H159" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="I159"/>
       <c r="J159"/>
@@ -4445,7 +4220,7 @@
         <v>44316</v>
       </c>
       <c r="B160" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C160"/>
       <c r="D160"/>
@@ -4453,7 +4228,7 @@
       <c r="F160"/>
       <c r="G160"/>
       <c r="H160" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="I160"/>
       <c r="J160"/>
@@ -4464,7 +4239,7 @@
         <v>44316</v>
       </c>
       <c r="B161" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C161"/>
       <c r="D161"/>
@@ -4472,7 +4247,7 @@
       <c r="F161"/>
       <c r="G161"/>
       <c r="H161" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="I161"/>
       <c r="J161"/>
@@ -4483,7 +4258,7 @@
         <v>44347</v>
       </c>
       <c r="B162" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C162"/>
       <c r="D162"/>
@@ -4491,7 +4266,7 @@
       <c r="F162"/>
       <c r="G162"/>
       <c r="H162" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="I162"/>
       <c r="J162"/>
@@ -4502,7 +4277,7 @@
         <v>44347</v>
       </c>
       <c r="B163" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C163"/>
       <c r="D163"/>
@@ -4510,7 +4285,7 @@
       <c r="F163"/>
       <c r="G163"/>
       <c r="H163" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="I163"/>
       <c r="J163"/>
@@ -4529,7 +4304,7 @@
       <c r="F164"/>
       <c r="G164"/>
       <c r="H164" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="I164"/>
       <c r="J164"/>
@@ -4540,7 +4315,7 @@
         <v>44347</v>
       </c>
       <c r="B165" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C165"/>
       <c r="D165"/>
@@ -4548,7 +4323,7 @@
       <c r="F165"/>
       <c r="G165"/>
       <c r="H165" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="I165"/>
       <c r="J165"/>
@@ -4567,7 +4342,7 @@
       <c r="F166"/>
       <c r="G166"/>
       <c r="H166" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="I166"/>
       <c r="J166"/>
@@ -4578,7 +4353,7 @@
         <v>44377</v>
       </c>
       <c r="B167" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C167"/>
       <c r="D167"/>
@@ -4586,7 +4361,7 @@
       <c r="F167"/>
       <c r="G167"/>
       <c r="H167" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="I167"/>
       <c r="J167"/>
@@ -4605,7 +4380,7 @@
       <c r="F168"/>
       <c r="G168"/>
       <c r="H168" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="I168"/>
       <c r="J168"/>
@@ -4616,7 +4391,7 @@
         <v>44377</v>
       </c>
       <c r="B169" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C169"/>
       <c r="D169"/>
@@ -4624,7 +4399,7 @@
       <c r="F169"/>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="I169"/>
       <c r="J169"/>
@@ -4643,7 +4418,7 @@
       <c r="F170"/>
       <c r="G170"/>
       <c r="H170" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="I170"/>
       <c r="J170"/>
@@ -4662,7 +4437,7 @@
       <c r="F171"/>
       <c r="G171"/>
       <c r="H171" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="I171"/>
       <c r="J171"/>
@@ -4681,7 +4456,7 @@
       <c r="F172"/>
       <c r="G172"/>
       <c r="H172" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="I172"/>
       <c r="J172"/>
@@ -4700,7 +4475,7 @@
       <c r="F173"/>
       <c r="G173"/>
       <c r="H173" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="I173"/>
       <c r="J173"/>
@@ -4711,7 +4486,7 @@
         <v>44439</v>
       </c>
       <c r="B174" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C174"/>
       <c r="D174"/>
@@ -4719,7 +4494,7 @@
       <c r="F174"/>
       <c r="G174"/>
       <c r="H174" t="s">
-        <v>172</v>
+        <v>121</v>
       </c>
       <c r="I174"/>
       <c r="J174"/>
@@ -4738,7 +4513,7 @@
       <c r="F175"/>
       <c r="G175"/>
       <c r="H175" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="I175"/>
       <c r="J175"/>
@@ -4757,7 +4532,7 @@
       <c r="F176"/>
       <c r="G176"/>
       <c r="H176" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="I176"/>
       <c r="J176"/>
@@ -4768,7 +4543,7 @@
         <v>44439</v>
       </c>
       <c r="B177" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C177"/>
       <c r="D177"/>
@@ -4776,7 +4551,7 @@
       <c r="F177"/>
       <c r="G177"/>
       <c r="H177" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="I177"/>
       <c r="J177"/>
@@ -4795,7 +4570,7 @@
       <c r="F178"/>
       <c r="G178"/>
       <c r="H178" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I178"/>
       <c r="J178"/>
@@ -4806,7 +4581,7 @@
         <v>44469</v>
       </c>
       <c r="B179" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C179"/>
       <c r="D179"/>
@@ -4814,7 +4589,7 @@
       <c r="F179"/>
       <c r="G179"/>
       <c r="H179" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="I179"/>
       <c r="J179"/>
@@ -4825,7 +4600,7 @@
         <v>44469</v>
       </c>
       <c r="B180" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C180"/>
       <c r="D180"/>
@@ -4833,7 +4608,7 @@
       <c r="F180"/>
       <c r="G180"/>
       <c r="H180" t="s">
-        <v>177</v>
+        <v>119</v>
       </c>
       <c r="I180"/>
       <c r="J180"/>
@@ -4852,7 +4627,7 @@
       <c r="F181"/>
       <c r="G181"/>
       <c r="H181" t="s">
-        <v>178</v>
+        <v>59</v>
       </c>
       <c r="I181"/>
       <c r="J181"/>
@@ -4863,7 +4638,7 @@
         <v>44500</v>
       </c>
       <c r="B182" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C182"/>
       <c r="D182"/>
@@ -4871,7 +4646,7 @@
       <c r="F182"/>
       <c r="G182"/>
       <c r="H182" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="I182"/>
       <c r="J182"/>
@@ -4882,7 +4657,7 @@
         <v>44500</v>
       </c>
       <c r="B183" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C183"/>
       <c r="D183"/>
@@ -4890,7 +4665,7 @@
       <c r="F183"/>
       <c r="G183"/>
       <c r="H183" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="I183"/>
       <c r="J183"/>
@@ -4901,7 +4676,7 @@
         <v>44500</v>
       </c>
       <c r="B184" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C184"/>
       <c r="D184"/>
@@ -4909,7 +4684,7 @@
       <c r="F184"/>
       <c r="G184"/>
       <c r="H184" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="I184"/>
       <c r="J184"/>
@@ -4920,7 +4695,7 @@
         <v>44500</v>
       </c>
       <c r="B185" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C185"/>
       <c r="D185"/>
@@ -4928,7 +4703,7 @@
       <c r="F185"/>
       <c r="G185"/>
       <c r="H185" t="s">
-        <v>182</v>
+        <v>55</v>
       </c>
       <c r="I185"/>
       <c r="J185"/>
@@ -4939,7 +4714,7 @@
         <v>44530</v>
       </c>
       <c r="B186" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C186"/>
       <c r="D186"/>
@@ -4947,7 +4722,7 @@
       <c r="F186"/>
       <c r="G186"/>
       <c r="H186" t="s">
-        <v>183</v>
+        <v>14</v>
       </c>
       <c r="I186"/>
       <c r="J186"/>
@@ -4958,7 +4733,7 @@
         <v>44530</v>
       </c>
       <c r="B187" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C187"/>
       <c r="D187"/>
@@ -4966,7 +4741,7 @@
       <c r="F187"/>
       <c r="G187"/>
       <c r="H187" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="I187"/>
       <c r="J187"/>
@@ -4977,7 +4752,7 @@
         <v>44530</v>
       </c>
       <c r="B188" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C188"/>
       <c r="D188"/>
@@ -4985,7 +4760,7 @@
       <c r="F188"/>
       <c r="G188"/>
       <c r="H188" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="I188"/>
       <c r="J188"/>
@@ -4996,7 +4771,7 @@
         <v>44530</v>
       </c>
       <c r="B189" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C189"/>
       <c r="D189"/>
@@ -5004,7 +4779,7 @@
       <c r="F189"/>
       <c r="G189"/>
       <c r="H189" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="I189"/>
       <c r="J189"/>
@@ -5015,7 +4790,7 @@
         <v>44561</v>
       </c>
       <c r="B190" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C190"/>
       <c r="D190"/>
@@ -5023,7 +4798,7 @@
       <c r="F190"/>
       <c r="G190"/>
       <c r="H190" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="I190"/>
       <c r="J190"/>
@@ -5034,7 +4809,7 @@
         <v>44561</v>
       </c>
       <c r="B191" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C191"/>
       <c r="D191"/>
@@ -5042,7 +4817,7 @@
       <c r="F191"/>
       <c r="G191"/>
       <c r="H191" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="I191"/>
       <c r="J191"/>
@@ -5053,7 +4828,7 @@
         <v>44561</v>
       </c>
       <c r="B192" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C192"/>
       <c r="D192"/>
@@ -5061,7 +4836,7 @@
       <c r="F192"/>
       <c r="G192"/>
       <c r="H192" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="I192"/>
       <c r="J192"/>
@@ -5072,7 +4847,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C193"/>
       <c r="D193"/>
@@ -5080,7 +4855,7 @@
       <c r="F193"/>
       <c r="G193"/>
       <c r="H193" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="I193"/>
       <c r="J193"/>
@@ -5099,7 +4874,7 @@
       <c r="F194"/>
       <c r="G194"/>
       <c r="H194" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="I194"/>
       <c r="J194"/>
@@ -5110,7 +4885,7 @@
         <v>44592</v>
       </c>
       <c r="B195" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C195"/>
       <c r="D195"/>
@@ -5118,7 +4893,7 @@
       <c r="F195"/>
       <c r="G195"/>
       <c r="H195" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="I195"/>
       <c r="J195"/>
@@ -5129,7 +4904,7 @@
         <v>44592</v>
       </c>
       <c r="B196" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C196"/>
       <c r="D196"/>
@@ -5137,7 +4912,7 @@
       <c r="F196"/>
       <c r="G196"/>
       <c r="H196" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="I196"/>
       <c r="J196"/>
@@ -5148,7 +4923,7 @@
         <v>44592</v>
       </c>
       <c r="B197" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C197"/>
       <c r="D197"/>
@@ -5156,7 +4931,7 @@
       <c r="F197"/>
       <c r="G197"/>
       <c r="H197" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="I197"/>
       <c r="J197"/>
@@ -5167,7 +4942,7 @@
         <v>44620</v>
       </c>
       <c r="B198" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C198"/>
       <c r="D198"/>
@@ -5175,7 +4950,7 @@
       <c r="F198"/>
       <c r="G198"/>
       <c r="H198" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="I198"/>
       <c r="J198"/>
@@ -5186,7 +4961,7 @@
         <v>44620</v>
       </c>
       <c r="B199" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C199"/>
       <c r="D199"/>
@@ -5194,7 +4969,7 @@
       <c r="F199"/>
       <c r="G199"/>
       <c r="H199" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="I199"/>
       <c r="J199"/>
@@ -5205,7 +4980,7 @@
         <v>44620</v>
       </c>
       <c r="B200" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C200"/>
       <c r="D200"/>
@@ -5213,7 +4988,7 @@
       <c r="F200"/>
       <c r="G200"/>
       <c r="H200" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="I200"/>
       <c r="J200"/>
@@ -5224,7 +4999,7 @@
         <v>44620</v>
       </c>
       <c r="B201" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C201"/>
       <c r="D201"/>
@@ -5232,7 +5007,7 @@
       <c r="F201"/>
       <c r="G201"/>
       <c r="H201" t="s">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="I201"/>
       <c r="J201"/>
@@ -5251,7 +5026,7 @@
       <c r="F202"/>
       <c r="G202"/>
       <c r="H202" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="I202"/>
       <c r="J202"/>
@@ -5270,7 +5045,7 @@
       <c r="F203"/>
       <c r="G203"/>
       <c r="H203" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="I203"/>
       <c r="J203"/>
@@ -5289,7 +5064,7 @@
       <c r="F204"/>
       <c r="G204"/>
       <c r="H204" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="I204"/>
       <c r="J204"/>
@@ -5308,7 +5083,7 @@
       <c r="F205"/>
       <c r="G205"/>
       <c r="H205" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="I205"/>
       <c r="J205"/>
@@ -5327,7 +5102,7 @@
       <c r="F206"/>
       <c r="G206"/>
       <c r="H206" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="I206"/>
       <c r="J206"/>
@@ -5346,7 +5121,7 @@
       <c r="F207"/>
       <c r="G207"/>
       <c r="H207" t="s">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="I207"/>
       <c r="J207"/>
@@ -5357,7 +5132,7 @@
         <v>44681</v>
       </c>
       <c r="B208" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C208"/>
       <c r="D208"/>
@@ -5365,7 +5140,7 @@
       <c r="F208"/>
       <c r="G208"/>
       <c r="H208" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="I208"/>
       <c r="J208"/>
@@ -5376,7 +5151,7 @@
         <v>44681</v>
       </c>
       <c r="B209" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C209"/>
       <c r="D209"/>
@@ -5384,7 +5159,7 @@
       <c r="F209"/>
       <c r="G209"/>
       <c r="H209" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="I209"/>
       <c r="J209"/>
@@ -5403,7 +5178,7 @@
       <c r="F210"/>
       <c r="G210"/>
       <c r="H210" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="I210"/>
       <c r="J210"/>
@@ -5414,7 +5189,7 @@
         <v>44712</v>
       </c>
       <c r="B211" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C211"/>
       <c r="D211"/>
@@ -5422,7 +5197,7 @@
       <c r="F211"/>
       <c r="G211"/>
       <c r="H211" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="I211"/>
       <c r="J211"/>
@@ -5433,7 +5208,7 @@
         <v>44712</v>
       </c>
       <c r="B212" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C212"/>
       <c r="D212"/>
@@ -5441,7 +5216,7 @@
       <c r="F212"/>
       <c r="G212"/>
       <c r="H212" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="I212"/>
       <c r="J212"/>
@@ -5452,7 +5227,7 @@
         <v>44712</v>
       </c>
       <c r="B213" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C213"/>
       <c r="D213"/>
@@ -5460,7 +5235,7 @@
       <c r="F213"/>
       <c r="G213"/>
       <c r="H213" t="s">
-        <v>23</v>
+        <v>124</v>
       </c>
       <c r="I213"/>
       <c r="J213"/>
@@ -5479,7 +5254,7 @@
       <c r="F214"/>
       <c r="G214"/>
       <c r="H214" t="s">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="I214"/>
       <c r="J214"/>
@@ -5490,7 +5265,7 @@
         <v>44742</v>
       </c>
       <c r="B215" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C215"/>
       <c r="D215"/>
@@ -5498,7 +5273,7 @@
       <c r="F215"/>
       <c r="G215"/>
       <c r="H215" t="s">
-        <v>205</v>
+        <v>89</v>
       </c>
       <c r="I215"/>
       <c r="J215"/>
@@ -5509,7 +5284,7 @@
         <v>44742</v>
       </c>
       <c r="B216" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C216"/>
       <c r="D216"/>
@@ -5517,7 +5292,7 @@
       <c r="F216"/>
       <c r="G216"/>
       <c r="H216" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="I216"/>
       <c r="J216"/>
@@ -5528,7 +5303,7 @@
         <v>44742</v>
       </c>
       <c r="B217" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C217"/>
       <c r="D217"/>
@@ -5536,7 +5311,7 @@
       <c r="F217"/>
       <c r="G217"/>
       <c r="H217" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="I217"/>
       <c r="J217"/>
@@ -5547,7 +5322,7 @@
         <v>44773</v>
       </c>
       <c r="B218" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C218"/>
       <c r="D218"/>
@@ -5555,7 +5330,7 @@
       <c r="F218"/>
       <c r="G218"/>
       <c r="H218" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="I218"/>
       <c r="J218"/>
@@ -5566,7 +5341,7 @@
         <v>44773</v>
       </c>
       <c r="B219" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C219"/>
       <c r="D219"/>
@@ -5574,7 +5349,7 @@
       <c r="F219"/>
       <c r="G219"/>
       <c r="H219" t="s">
-        <v>209</v>
+        <v>166</v>
       </c>
       <c r="I219"/>
       <c r="J219"/>
@@ -5593,7 +5368,7 @@
       <c r="F220"/>
       <c r="G220"/>
       <c r="H220" t="s">
-        <v>210</v>
+        <v>86</v>
       </c>
       <c r="I220"/>
       <c r="J220"/>
@@ -5612,7 +5387,7 @@
       <c r="F221"/>
       <c r="G221"/>
       <c r="H221" t="s">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="I221"/>
       <c r="J221"/>
@@ -5623,7 +5398,7 @@
         <v>44804</v>
       </c>
       <c r="B222" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C222"/>
       <c r="D222"/>
@@ -5631,7 +5406,7 @@
       <c r="F222"/>
       <c r="G222"/>
       <c r="H222" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="I222"/>
       <c r="J222"/>
@@ -5642,7 +5417,7 @@
         <v>44804</v>
       </c>
       <c r="B223" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C223"/>
       <c r="D223"/>
@@ -5650,7 +5425,7 @@
       <c r="F223"/>
       <c r="G223"/>
       <c r="H223" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="I223"/>
       <c r="J223"/>
@@ -5661,7 +5436,7 @@
         <v>44804</v>
       </c>
       <c r="B224" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C224"/>
       <c r="D224"/>
@@ -5669,7 +5444,7 @@
       <c r="F224"/>
       <c r="G224"/>
       <c r="H224" t="s">
-        <v>23</v>
+        <v>182</v>
       </c>
       <c r="I224"/>
       <c r="J224"/>
@@ -5680,7 +5455,7 @@
         <v>44804</v>
       </c>
       <c r="B225" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C225"/>
       <c r="D225"/>
@@ -5688,7 +5463,7 @@
       <c r="F225"/>
       <c r="G225"/>
       <c r="H225" t="s">
-        <v>214</v>
+        <v>53</v>
       </c>
       <c r="I225"/>
       <c r="J225"/>
@@ -5699,7 +5474,7 @@
         <v>44834</v>
       </c>
       <c r="B226" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C226"/>
       <c r="D226"/>
@@ -5707,7 +5482,7 @@
       <c r="F226"/>
       <c r="G226"/>
       <c r="H226" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="I226"/>
       <c r="J226"/>
@@ -5726,7 +5501,7 @@
       <c r="F227"/>
       <c r="G227"/>
       <c r="H227" t="s">
-        <v>104</v>
+        <v>184</v>
       </c>
       <c r="I227"/>
       <c r="J227"/>
@@ -5737,7 +5512,7 @@
         <v>44834</v>
       </c>
       <c r="B228" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C228"/>
       <c r="D228"/>
@@ -5745,7 +5520,7 @@
       <c r="F228"/>
       <c r="G228"/>
       <c r="H228" t="s">
-        <v>216</v>
+        <v>131</v>
       </c>
       <c r="I228"/>
       <c r="J228"/>
@@ -5756,7 +5531,7 @@
         <v>44834</v>
       </c>
       <c r="B229" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C229"/>
       <c r="D229"/>
@@ -5764,7 +5539,7 @@
       <c r="F229"/>
       <c r="G229"/>
       <c r="H229" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="I229"/>
       <c r="J229"/>
@@ -5783,7 +5558,7 @@
       <c r="F230"/>
       <c r="G230"/>
       <c r="H230" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="I230"/>
       <c r="J230"/>
@@ -5794,7 +5569,7 @@
         <v>44865</v>
       </c>
       <c r="B231" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C231"/>
       <c r="D231"/>
@@ -5802,7 +5577,7 @@
       <c r="F231"/>
       <c r="G231"/>
       <c r="H231" t="s">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="I231"/>
       <c r="J231"/>
@@ -5813,7 +5588,7 @@
         <v>44865</v>
       </c>
       <c r="B232" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C232"/>
       <c r="D232"/>
@@ -5821,7 +5596,7 @@
       <c r="F232"/>
       <c r="G232"/>
       <c r="H232" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="I232"/>
       <c r="J232"/>
@@ -5832,7 +5607,7 @@
         <v>44865</v>
       </c>
       <c r="B233" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C233"/>
       <c r="D233"/>
@@ -5840,7 +5615,7 @@
       <c r="F233"/>
       <c r="G233"/>
       <c r="H233" t="s">
-        <v>46</v>
+        <v>189</v>
       </c>
       <c r="I233"/>
       <c r="J233"/>
@@ -5851,7 +5626,7 @@
         <v>44895</v>
       </c>
       <c r="B234" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C234"/>
       <c r="D234"/>
@@ -5859,7 +5634,7 @@
       <c r="F234"/>
       <c r="G234"/>
       <c r="H234" t="s">
-        <v>220</v>
+        <v>35</v>
       </c>
       <c r="I234"/>
       <c r="J234"/>
@@ -5870,7 +5645,7 @@
         <v>44895</v>
       </c>
       <c r="B235" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C235"/>
       <c r="D235"/>
@@ -5878,7 +5653,7 @@
       <c r="F235"/>
       <c r="G235"/>
       <c r="H235" t="s">
-        <v>221</v>
+        <v>60</v>
       </c>
       <c r="I235"/>
       <c r="J235"/>
@@ -5889,7 +5664,7 @@
         <v>44895</v>
       </c>
       <c r="B236" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C236"/>
       <c r="D236"/>
@@ -5897,7 +5672,7 @@
       <c r="F236"/>
       <c r="G236"/>
       <c r="H236" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="I236"/>
       <c r="J236"/>
@@ -5908,7 +5683,7 @@
         <v>44895</v>
       </c>
       <c r="B237" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C237"/>
       <c r="D237"/>
@@ -5916,7 +5691,7 @@
       <c r="F237"/>
       <c r="G237"/>
       <c r="H237" t="s">
-        <v>223</v>
+        <v>58</v>
       </c>
       <c r="I237"/>
       <c r="J237"/>
@@ -5935,7 +5710,7 @@
       <c r="F238"/>
       <c r="G238"/>
       <c r="H238" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="I238"/>
       <c r="J238"/>
@@ -5946,7 +5721,7 @@
         <v>44926</v>
       </c>
       <c r="B239" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C239"/>
       <c r="D239"/>
@@ -5954,7 +5729,7 @@
       <c r="F239"/>
       <c r="G239"/>
       <c r="H239" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="I239"/>
       <c r="J239"/>
@@ -5973,7 +5748,7 @@
       <c r="F240"/>
       <c r="G240"/>
       <c r="H240" t="s">
-        <v>226</v>
+        <v>53</v>
       </c>
       <c r="I240"/>
       <c r="J240"/>
@@ -5984,7 +5759,7 @@
         <v>44926</v>
       </c>
       <c r="B241" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C241"/>
       <c r="D241"/>
@@ -5992,7 +5767,7 @@
       <c r="F241"/>
       <c r="G241"/>
       <c r="H241" t="s">
-        <v>227</v>
+        <v>180</v>
       </c>
       <c r="I241"/>
       <c r="J241"/>
@@ -6003,7 +5778,7 @@
         <v>44957</v>
       </c>
       <c r="B242" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C242"/>
       <c r="D242"/>
@@ -6011,7 +5786,7 @@
       <c r="F242"/>
       <c r="G242"/>
       <c r="H242" t="s">
-        <v>228</v>
+        <v>88</v>
       </c>
       <c r="I242"/>
       <c r="J242"/>
@@ -6022,7 +5797,7 @@
         <v>44957</v>
       </c>
       <c r="B243" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C243"/>
       <c r="D243"/>
@@ -6030,7 +5805,7 @@
       <c r="F243"/>
       <c r="G243"/>
       <c r="H243" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="I243"/>
       <c r="J243"/>
@@ -6041,7 +5816,7 @@
         <v>44957</v>
       </c>
       <c r="B244" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C244"/>
       <c r="D244"/>
@@ -6049,7 +5824,7 @@
       <c r="F244"/>
       <c r="G244"/>
       <c r="H244" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="I244"/>
       <c r="J244"/>
@@ -6060,7 +5835,7 @@
         <v>44957</v>
       </c>
       <c r="B245" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C245"/>
       <c r="D245"/>
@@ -6068,7 +5843,7 @@
       <c r="F245"/>
       <c r="G245"/>
       <c r="H245" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="I245"/>
       <c r="J245"/>
@@ -6079,7 +5854,7 @@
         <v>44985</v>
       </c>
       <c r="B246" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C246"/>
       <c r="D246"/>
@@ -6087,7 +5862,7 @@
       <c r="F246"/>
       <c r="G246"/>
       <c r="H246" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="I246"/>
       <c r="J246"/>
@@ -6106,7 +5881,7 @@
       <c r="F247"/>
       <c r="G247"/>
       <c r="H247" t="s">
-        <v>232</v>
+        <v>23</v>
       </c>
       <c r="I247"/>
       <c r="J247"/>
@@ -6117,7 +5892,7 @@
         <v>44985</v>
       </c>
       <c r="B248" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C248"/>
       <c r="D248"/>
@@ -6125,7 +5900,7 @@
       <c r="F248"/>
       <c r="G248"/>
       <c r="H248" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="I248"/>
       <c r="J248"/>
@@ -6144,7 +5919,7 @@
       <c r="F249"/>
       <c r="G249"/>
       <c r="H249" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="I249"/>
       <c r="J249"/>
@@ -6155,7 +5930,7 @@
         <v>45016</v>
       </c>
       <c r="B250" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C250"/>
       <c r="D250"/>
@@ -6163,7 +5938,7 @@
       <c r="F250"/>
       <c r="G250"/>
       <c r="H250" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="I250"/>
       <c r="J250"/>
@@ -6182,7 +5957,7 @@
       <c r="F251"/>
       <c r="G251"/>
       <c r="H251" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="I251"/>
       <c r="J251"/>
@@ -6193,7 +5968,7 @@
         <v>45016</v>
       </c>
       <c r="B252" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C252"/>
       <c r="D252"/>
@@ -6201,7 +5976,7 @@
       <c r="F252"/>
       <c r="G252"/>
       <c r="H252" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="I252"/>
       <c r="J252"/>
@@ -6212,7 +5987,7 @@
         <v>45016</v>
       </c>
       <c r="B253" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C253"/>
       <c r="D253"/>
@@ -6220,7 +5995,7 @@
       <c r="F253"/>
       <c r="G253"/>
       <c r="H253" t="s">
-        <v>236</v>
+        <v>159</v>
       </c>
       <c r="I253"/>
       <c r="J253"/>
@@ -6239,7 +6014,7 @@
       <c r="F254"/>
       <c r="G254"/>
       <c r="H254" t="s">
-        <v>237</v>
+        <v>86</v>
       </c>
       <c r="I254"/>
       <c r="J254"/>
@@ -6250,7 +6025,7 @@
         <v>45046</v>
       </c>
       <c r="B255" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C255"/>
       <c r="D255"/>
@@ -6258,7 +6033,7 @@
       <c r="F255"/>
       <c r="G255"/>
       <c r="H255" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I255"/>
       <c r="J255"/>
@@ -6269,7 +6044,7 @@
         <v>45046</v>
       </c>
       <c r="B256" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C256"/>
       <c r="D256"/>
@@ -6277,7 +6052,7 @@
       <c r="F256"/>
       <c r="G256"/>
       <c r="H256" t="s">
-        <v>238</v>
+        <v>200</v>
       </c>
       <c r="I256"/>
       <c r="J256"/>
@@ -6288,7 +6063,7 @@
         <v>45046</v>
       </c>
       <c r="B257" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C257"/>
       <c r="D257"/>
@@ -6296,7 +6071,7 @@
       <c r="F257"/>
       <c r="G257"/>
       <c r="H257" t="s">
-        <v>90</v>
+        <v>201</v>
       </c>
       <c r="I257"/>
       <c r="J257"/>
@@ -6307,7 +6082,7 @@
         <v>45077</v>
       </c>
       <c r="B258" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C258"/>
       <c r="D258"/>
@@ -6315,7 +6090,7 @@
       <c r="F258"/>
       <c r="G258"/>
       <c r="H258" t="s">
-        <v>239</v>
+        <v>114</v>
       </c>
       <c r="I258"/>
       <c r="J258"/>
@@ -6326,7 +6101,7 @@
         <v>45077</v>
       </c>
       <c r="B259" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C259"/>
       <c r="D259"/>
@@ -6334,7 +6109,7 @@
       <c r="F259"/>
       <c r="G259"/>
       <c r="H259" t="s">
-        <v>14</v>
+        <v>202</v>
       </c>
       <c r="I259"/>
       <c r="J259"/>
@@ -6345,7 +6120,7 @@
         <v>45077</v>
       </c>
       <c r="B260" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C260"/>
       <c r="D260"/>
@@ -6353,7 +6128,7 @@
       <c r="F260"/>
       <c r="G260"/>
       <c r="H260" t="s">
-        <v>240</v>
+        <v>89</v>
       </c>
       <c r="I260"/>
       <c r="J260"/>
@@ -6372,7 +6147,7 @@
       <c r="F261"/>
       <c r="G261"/>
       <c r="H261" t="s">
-        <v>241</v>
+        <v>26</v>
       </c>
       <c r="I261"/>
       <c r="J261"/>
@@ -6391,7 +6166,7 @@
       <c r="F262"/>
       <c r="G262"/>
       <c r="H262" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="I262"/>
       <c r="J262"/>
@@ -6410,7 +6185,7 @@
       <c r="F263"/>
       <c r="G263"/>
       <c r="H263" t="s">
-        <v>242</v>
+        <v>16</v>
       </c>
       <c r="I263"/>
       <c r="J263"/>
@@ -6429,7 +6204,7 @@
       <c r="F264"/>
       <c r="G264"/>
       <c r="H264" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="I264"/>
       <c r="J264"/>
@@ -6448,7 +6223,7 @@
       <c r="F265"/>
       <c r="G265"/>
       <c r="H265" t="s">
-        <v>244</v>
+        <v>42</v>
       </c>
       <c r="I265"/>
       <c r="J265"/>
@@ -6459,7 +6234,7 @@
         <v>45138</v>
       </c>
       <c r="B266" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C266"/>
       <c r="D266"/>
@@ -6467,7 +6242,7 @@
       <c r="F266"/>
       <c r="G266"/>
       <c r="H266" t="s">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="I266"/>
       <c r="J266"/>
@@ -6478,7 +6253,7 @@
         <v>45138</v>
       </c>
       <c r="B267" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C267"/>
       <c r="D267"/>
@@ -6486,7 +6261,7 @@
       <c r="F267"/>
       <c r="G267"/>
       <c r="H267" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
       <c r="I267"/>
       <c r="J267"/>
@@ -6505,7 +6280,7 @@
       <c r="F268"/>
       <c r="G268"/>
       <c r="H268" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="I268"/>
       <c r="J268"/>
@@ -6516,7 +6291,7 @@
         <v>45138</v>
       </c>
       <c r="B269" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C269"/>
       <c r="D269"/>
@@ -6524,7 +6299,7 @@
       <c r="F269"/>
       <c r="G269"/>
       <c r="H269" t="s">
-        <v>247</v>
+        <v>24</v>
       </c>
       <c r="I269"/>
       <c r="J269"/>
@@ -6543,7 +6318,7 @@
       <c r="F270"/>
       <c r="G270"/>
       <c r="H270" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="I270"/>
       <c r="J270"/>
@@ -6554,7 +6329,7 @@
         <v>45169</v>
       </c>
       <c r="B271" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C271"/>
       <c r="D271"/>
@@ -6562,7 +6337,7 @@
       <c r="F271"/>
       <c r="G271"/>
       <c r="H271" t="s">
-        <v>74</v>
+        <v>208</v>
       </c>
       <c r="I271"/>
       <c r="J271"/>
@@ -6573,7 +6348,7 @@
         <v>45169</v>
       </c>
       <c r="B272" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C272"/>
       <c r="D272"/>
@@ -6581,7 +6356,7 @@
       <c r="F272"/>
       <c r="G272"/>
       <c r="H272" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="I272"/>
       <c r="J272"/>
@@ -6592,7 +6367,7 @@
         <v>45169</v>
       </c>
       <c r="B273" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C273"/>
       <c r="D273"/>
@@ -6600,7 +6375,7 @@
       <c r="F273"/>
       <c r="G273"/>
       <c r="H273" t="s">
-        <v>250</v>
+        <v>141</v>
       </c>
       <c r="I273"/>
       <c r="J273"/>
@@ -6611,7 +6386,7 @@
         <v>45199</v>
       </c>
       <c r="B274" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C274"/>
       <c r="D274"/>
@@ -6619,7 +6394,7 @@
       <c r="F274"/>
       <c r="G274"/>
       <c r="H274" t="s">
-        <v>251</v>
+        <v>45</v>
       </c>
       <c r="I274"/>
       <c r="J274"/>
@@ -6630,7 +6405,7 @@
         <v>45199</v>
       </c>
       <c r="B275" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C275"/>
       <c r="D275"/>
@@ -6638,7 +6413,7 @@
       <c r="F275"/>
       <c r="G275"/>
       <c r="H275" t="s">
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="I275"/>
       <c r="J275"/>
@@ -6649,7 +6424,7 @@
         <v>45199</v>
       </c>
       <c r="B276" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C276"/>
       <c r="D276"/>
@@ -6657,7 +6432,7 @@
       <c r="F276"/>
       <c r="G276"/>
       <c r="H276" t="s">
-        <v>74</v>
+        <v>194</v>
       </c>
       <c r="I276"/>
       <c r="J276"/>
@@ -6676,7 +6451,7 @@
       <c r="F277"/>
       <c r="G277"/>
       <c r="H277" t="s">
-        <v>63</v>
+        <v>211</v>
       </c>
       <c r="I277"/>
       <c r="J277"/>
@@ -6687,7 +6462,7 @@
         <v>45230</v>
       </c>
       <c r="B278" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C278"/>
       <c r="D278"/>
@@ -6695,7 +6470,7 @@
       <c r="F278"/>
       <c r="G278"/>
       <c r="H278" t="s">
-        <v>253</v>
+        <v>195</v>
       </c>
       <c r="I278"/>
       <c r="J278"/>
@@ -6714,7 +6489,7 @@
       <c r="F279"/>
       <c r="G279"/>
       <c r="H279" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="I279"/>
       <c r="J279"/>
@@ -6725,7 +6500,7 @@
         <v>45230</v>
       </c>
       <c r="B280" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C280"/>
       <c r="D280"/>
@@ -6733,7 +6508,7 @@
       <c r="F280"/>
       <c r="G280"/>
       <c r="H280" t="s">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="I280"/>
       <c r="J280"/>
@@ -6744,7 +6519,7 @@
         <v>45230</v>
       </c>
       <c r="B281" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C281"/>
       <c r="D281"/>
@@ -6752,7 +6527,7 @@
       <c r="F281"/>
       <c r="G281"/>
       <c r="H281" t="s">
-        <v>255</v>
+        <v>180</v>
       </c>
       <c r="I281"/>
       <c r="J281"/>
@@ -6763,7 +6538,7 @@
         <v>45260</v>
       </c>
       <c r="B282" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C282"/>
       <c r="D282"/>
@@ -6771,7 +6546,7 @@
       <c r="F282"/>
       <c r="G282"/>
       <c r="H282" t="s">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="I282"/>
       <c r="J282"/>
@@ -6782,7 +6557,7 @@
         <v>45260</v>
       </c>
       <c r="B283" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C283"/>
       <c r="D283"/>
@@ -6790,7 +6565,7 @@
       <c r="F283"/>
       <c r="G283"/>
       <c r="H283" t="s">
-        <v>257</v>
+        <v>215</v>
       </c>
       <c r="I283"/>
       <c r="J283"/>
@@ -6801,7 +6576,7 @@
         <v>45260</v>
       </c>
       <c r="B284" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C284"/>
       <c r="D284"/>
@@ -6809,7 +6584,7 @@
       <c r="F284"/>
       <c r="G284"/>
       <c r="H284" t="s">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="I284"/>
       <c r="J284"/>
@@ -6820,7 +6595,7 @@
         <v>45260</v>
       </c>
       <c r="B285" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C285"/>
       <c r="D285"/>
@@ -6828,7 +6603,7 @@
       <c r="F285"/>
       <c r="G285"/>
       <c r="H285" t="s">
-        <v>258</v>
+        <v>60</v>
       </c>
       <c r="I285"/>
       <c r="J285"/>
@@ -6839,7 +6614,7 @@
         <v>45291</v>
       </c>
       <c r="B286" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C286"/>
       <c r="D286"/>
@@ -6847,7 +6622,7 @@
       <c r="F286"/>
       <c r="G286"/>
       <c r="H286" t="s">
-        <v>113</v>
+        <v>217</v>
       </c>
       <c r="I286"/>
       <c r="J286"/>
@@ -6858,7 +6633,7 @@
         <v>45291</v>
       </c>
       <c r="B287" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C287"/>
       <c r="D287"/>
@@ -6866,7 +6641,7 @@
       <c r="F287"/>
       <c r="G287"/>
       <c r="H287" t="s">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="I287"/>
       <c r="J287"/>
@@ -6877,7 +6652,7 @@
         <v>45291</v>
       </c>
       <c r="B288" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C288"/>
       <c r="D288"/>
@@ -6885,7 +6660,7 @@
       <c r="F288"/>
       <c r="G288"/>
       <c r="H288" t="s">
-        <v>259</v>
+        <v>219</v>
       </c>
       <c r="I288"/>
       <c r="J288"/>
@@ -6896,7 +6671,7 @@
         <v>45291</v>
       </c>
       <c r="B289" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C289"/>
       <c r="D289"/>
@@ -6904,7 +6679,7 @@
       <c r="F289"/>
       <c r="G289"/>
       <c r="H289" t="s">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="I289"/>
       <c r="J289"/>
@@ -6915,7 +6690,7 @@
         <v>45322</v>
       </c>
       <c r="B290" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C290"/>
       <c r="D290"/>
@@ -6923,7 +6698,7 @@
       <c r="F290"/>
       <c r="G290"/>
       <c r="H290" t="s">
-        <v>172</v>
+        <v>61</v>
       </c>
       <c r="I290"/>
       <c r="J290"/>
@@ -6934,7 +6709,7 @@
         <v>45322</v>
       </c>
       <c r="B291" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C291"/>
       <c r="D291"/>
@@ -6942,7 +6717,7 @@
       <c r="F291"/>
       <c r="G291"/>
       <c r="H291" t="s">
-        <v>261</v>
+        <v>83</v>
       </c>
       <c r="I291"/>
       <c r="J291"/>
@@ -6961,7 +6736,7 @@
       <c r="F292"/>
       <c r="G292"/>
       <c r="H292" t="s">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="I292"/>
       <c r="J292"/>
@@ -6972,7 +6747,7 @@
         <v>45322</v>
       </c>
       <c r="B293" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C293"/>
       <c r="D293"/>
@@ -6980,7 +6755,7 @@
       <c r="F293"/>
       <c r="G293"/>
       <c r="H293" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="I293"/>
       <c r="J293"/>
@@ -6991,7 +6766,7 @@
         <v>45351</v>
       </c>
       <c r="B294" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C294"/>
       <c r="D294"/>
@@ -6999,7 +6774,7 @@
       <c r="F294"/>
       <c r="G294"/>
       <c r="H294" t="s">
-        <v>264</v>
+        <v>160</v>
       </c>
       <c r="I294"/>
       <c r="J294"/>
@@ -7010,7 +6785,7 @@
         <v>45351</v>
       </c>
       <c r="B295" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C295"/>
       <c r="D295"/>
@@ -7018,7 +6793,7 @@
       <c r="F295"/>
       <c r="G295"/>
       <c r="H295" t="s">
-        <v>265</v>
+        <v>222</v>
       </c>
       <c r="I295"/>
       <c r="J295"/>
@@ -7037,7 +6812,7 @@
       <c r="F296"/>
       <c r="G296"/>
       <c r="H296" t="s">
-        <v>266</v>
+        <v>49</v>
       </c>
       <c r="I296"/>
       <c r="J296"/>
@@ -7048,7 +6823,7 @@
         <v>45351</v>
       </c>
       <c r="B297" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C297"/>
       <c r="D297"/>
@@ -7056,7 +6831,7 @@
       <c r="F297"/>
       <c r="G297"/>
       <c r="H297" t="s">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="I297"/>
       <c r="J297"/>
@@ -7067,7 +6842,7 @@
         <v>45382</v>
       </c>
       <c r="B298" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C298"/>
       <c r="D298"/>
@@ -7075,7 +6850,7 @@
       <c r="F298"/>
       <c r="G298"/>
       <c r="H298" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I298"/>
       <c r="J298"/>
@@ -7086,7 +6861,7 @@
         <v>45382</v>
       </c>
       <c r="B299" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C299"/>
       <c r="D299"/>
@@ -7094,7 +6869,7 @@
       <c r="F299"/>
       <c r="G299"/>
       <c r="H299" t="s">
-        <v>268</v>
+        <v>77</v>
       </c>
       <c r="I299"/>
       <c r="J299"/>
@@ -7113,7 +6888,7 @@
       <c r="F300"/>
       <c r="G300"/>
       <c r="H300" t="s">
-        <v>269</v>
+        <v>224</v>
       </c>
       <c r="I300"/>
       <c r="J300"/>
@@ -7124,7 +6899,7 @@
         <v>45382</v>
       </c>
       <c r="B301" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C301"/>
       <c r="D301"/>
@@ -7132,7 +6907,7 @@
       <c r="F301"/>
       <c r="G301"/>
       <c r="H301" t="s">
-        <v>270</v>
+        <v>173</v>
       </c>
       <c r="I301"/>
       <c r="J301"/>
@@ -7151,7 +6926,7 @@
       <c r="F302"/>
       <c r="G302"/>
       <c r="H302" t="s">
-        <v>104</v>
+        <v>225</v>
       </c>
       <c r="I302"/>
       <c r="J302"/>
@@ -7170,7 +6945,7 @@
       <c r="F303"/>
       <c r="G303"/>
       <c r="H303" t="s">
-        <v>72</v>
+        <v>226</v>
       </c>
       <c r="I303"/>
       <c r="J303"/>
@@ -7189,7 +6964,7 @@
       <c r="F304"/>
       <c r="G304"/>
       <c r="H304" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="I304"/>
       <c r="J304"/>
@@ -7208,7 +6983,7 @@
       <c r="F305"/>
       <c r="G305"/>
       <c r="H305" t="s">
-        <v>272</v>
+        <v>20</v>
       </c>
       <c r="I305"/>
       <c r="J305"/>
@@ -7219,7 +6994,7 @@
         <v>45443</v>
       </c>
       <c r="B306" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C306"/>
       <c r="D306"/>
@@ -7227,7 +7002,7 @@
       <c r="F306"/>
       <c r="G306"/>
       <c r="H306" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="I306"/>
       <c r="J306"/>
@@ -7246,7 +7021,7 @@
       <c r="F307"/>
       <c r="G307"/>
       <c r="H307" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="I307"/>
       <c r="J307"/>
@@ -7257,7 +7032,7 @@
         <v>45443</v>
       </c>
       <c r="B308" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C308"/>
       <c r="D308"/>
@@ -7265,7 +7040,7 @@
       <c r="F308"/>
       <c r="G308"/>
       <c r="H308" t="s">
-        <v>274</v>
+        <v>173</v>
       </c>
       <c r="I308"/>
       <c r="J308"/>
@@ -7276,7 +7051,7 @@
         <v>45443</v>
       </c>
       <c r="B309" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C309"/>
       <c r="D309"/>
@@ -7284,7 +7059,7 @@
       <c r="F309"/>
       <c r="G309"/>
       <c r="H309" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="I309"/>
       <c r="J309"/>
@@ -7295,7 +7070,7 @@
         <v>45473</v>
       </c>
       <c r="B310" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C310"/>
       <c r="D310"/>
@@ -7303,7 +7078,7 @@
       <c r="F310"/>
       <c r="G310"/>
       <c r="H310" t="s">
-        <v>275</v>
+        <v>45</v>
       </c>
       <c r="I310"/>
       <c r="J310"/>
@@ -7314,7 +7089,7 @@
         <v>45473</v>
       </c>
       <c r="B311" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C311"/>
       <c r="D311"/>
@@ -7322,7 +7097,7 @@
       <c r="F311"/>
       <c r="G311"/>
       <c r="H311" t="s">
-        <v>276</v>
+        <v>229</v>
       </c>
       <c r="I311"/>
       <c r="J311"/>
@@ -7333,7 +7108,7 @@
         <v>45473</v>
       </c>
       <c r="B312" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C312"/>
       <c r="D312"/>
@@ -7341,7 +7116,7 @@
       <c r="F312"/>
       <c r="G312"/>
       <c r="H312" t="s">
-        <v>277</v>
+        <v>171</v>
       </c>
       <c r="I312"/>
       <c r="J312"/>
@@ -7352,7 +7127,7 @@
         <v>45473</v>
       </c>
       <c r="B313" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C313"/>
       <c r="D313"/>
@@ -7360,7 +7135,7 @@
       <c r="F313"/>
       <c r="G313"/>
       <c r="H313" t="s">
-        <v>93</v>
+        <v>230</v>
       </c>
       <c r="I313"/>
       <c r="J313"/>
@@ -7379,7 +7154,7 @@
       <c r="F314"/>
       <c r="G314"/>
       <c r="H314" t="s">
-        <v>74</v>
+        <v>184</v>
       </c>
       <c r="I314"/>
       <c r="J314"/>
@@ -7390,7 +7165,7 @@
         <v>45504</v>
       </c>
       <c r="B315" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C315"/>
       <c r="D315"/>
@@ -7398,7 +7173,7 @@
       <c r="F315"/>
       <c r="G315"/>
       <c r="H315" t="s">
-        <v>278</v>
+        <v>80</v>
       </c>
       <c r="I315"/>
       <c r="J315"/>
@@ -7409,7 +7184,7 @@
         <v>45504</v>
       </c>
       <c r="B316" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C316"/>
       <c r="D316"/>
@@ -7417,7 +7192,7 @@
       <c r="F316"/>
       <c r="G316"/>
       <c r="H316" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="I316"/>
       <c r="J316"/>
@@ -7428,7 +7203,7 @@
         <v>45504</v>
       </c>
       <c r="B317" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C317"/>
       <c r="D317"/>
@@ -7436,7 +7211,7 @@
       <c r="F317"/>
       <c r="G317"/>
       <c r="H317" t="s">
-        <v>279</v>
+        <v>232</v>
       </c>
       <c r="I317"/>
       <c r="J317"/>
@@ -7455,7 +7230,7 @@
       <c r="F318"/>
       <c r="G318"/>
       <c r="H318" t="s">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="I318"/>
       <c r="J318"/>
@@ -7466,7 +7241,7 @@
         <v>45535</v>
       </c>
       <c r="B319" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C319"/>
       <c r="D319"/>
@@ -7474,7 +7249,7 @@
       <c r="F319"/>
       <c r="G319"/>
       <c r="H319" t="s">
-        <v>280</v>
+        <v>184</v>
       </c>
       <c r="I319"/>
       <c r="J319"/>
@@ -7493,7 +7268,7 @@
       <c r="F320"/>
       <c r="G320"/>
       <c r="H320" t="s">
-        <v>73</v>
+        <v>233</v>
       </c>
       <c r="I320"/>
       <c r="J320"/>
@@ -7504,7 +7279,7 @@
         <v>45535</v>
       </c>
       <c r="B321" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C321"/>
       <c r="D321"/>
@@ -7512,7 +7287,7 @@
       <c r="F321"/>
       <c r="G321"/>
       <c r="H321" t="s">
-        <v>74</v>
+        <v>234</v>
       </c>
       <c r="I321"/>
       <c r="J321"/>
@@ -7531,7 +7306,7 @@
       <c r="F322"/>
       <c r="G322"/>
       <c r="H322" t="s">
-        <v>281</v>
+        <v>220</v>
       </c>
       <c r="I322"/>
       <c r="J322"/>
@@ -7550,7 +7325,7 @@
       <c r="F323"/>
       <c r="G323"/>
       <c r="H323" t="s">
-        <v>282</v>
+        <v>46</v>
       </c>
       <c r="I323"/>
       <c r="J323"/>
@@ -7569,7 +7344,7 @@
       <c r="F324"/>
       <c r="G324"/>
       <c r="H324" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="I324"/>
       <c r="J324"/>
@@ -7588,7 +7363,7 @@
       <c r="F325"/>
       <c r="G325"/>
       <c r="H325" t="s">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="I325"/>
       <c r="J325"/>
@@ -7599,7 +7374,7 @@
         <v>45596</v>
       </c>
       <c r="B326" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C326"/>
       <c r="D326"/>
@@ -7607,7 +7382,7 @@
       <c r="F326"/>
       <c r="G326"/>
       <c r="H326" t="s">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="I326"/>
       <c r="J326"/>
@@ -7618,7 +7393,7 @@
         <v>45596</v>
       </c>
       <c r="B327" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C327"/>
       <c r="D327"/>
@@ -7626,7 +7401,7 @@
       <c r="F327"/>
       <c r="G327"/>
       <c r="H327" t="s">
-        <v>285</v>
+        <v>63</v>
       </c>
       <c r="I327"/>
       <c r="J327"/>
@@ -7645,7 +7420,7 @@
       <c r="F328"/>
       <c r="G328"/>
       <c r="H328" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="I328"/>
       <c r="J328"/>
@@ -7656,7 +7431,7 @@
         <v>45596</v>
       </c>
       <c r="B329" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C329"/>
       <c r="D329"/>
@@ -7664,7 +7439,7 @@
       <c r="F329"/>
       <c r="G329"/>
       <c r="H329" t="s">
-        <v>287</v>
+        <v>238</v>
       </c>
       <c r="I329"/>
       <c r="J329"/>
@@ -7675,7 +7450,7 @@
         <v>45626</v>
       </c>
       <c r="B330" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C330"/>
       <c r="D330"/>
@@ -7683,7 +7458,7 @@
       <c r="F330"/>
       <c r="G330"/>
       <c r="H330" t="s">
-        <v>288</v>
+        <v>101</v>
       </c>
       <c r="I330"/>
       <c r="J330"/>
@@ -7702,7 +7477,7 @@
       <c r="F331"/>
       <c r="G331"/>
       <c r="H331" t="s">
-        <v>289</v>
+        <v>221</v>
       </c>
       <c r="I331"/>
       <c r="J331"/>
@@ -7721,7 +7496,7 @@
       <c r="F332"/>
       <c r="G332"/>
       <c r="H332" t="s">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="I332"/>
       <c r="J332"/>
@@ -7732,7 +7507,7 @@
         <v>45626</v>
       </c>
       <c r="B333" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C333"/>
       <c r="D333"/>
@@ -7740,7 +7515,7 @@
       <c r="F333"/>
       <c r="G333"/>
       <c r="H333" t="s">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="I333"/>
       <c r="J333"/>
@@ -7751,7 +7526,7 @@
         <v>45657</v>
       </c>
       <c r="B334" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C334"/>
       <c r="D334"/>
@@ -7759,7 +7534,7 @@
       <c r="F334"/>
       <c r="G334"/>
       <c r="H334" t="s">
-        <v>291</v>
+        <v>35</v>
       </c>
       <c r="I334"/>
       <c r="J334"/>
@@ -7778,7 +7553,7 @@
       <c r="F335"/>
       <c r="G335"/>
       <c r="H335" t="s">
-        <v>127</v>
+        <v>240</v>
       </c>
       <c r="I335"/>
       <c r="J335"/>
@@ -7789,7 +7564,7 @@
         <v>45657</v>
       </c>
       <c r="B336" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C336"/>
       <c r="D336"/>
@@ -7797,7 +7572,7 @@
       <c r="F336"/>
       <c r="G336"/>
       <c r="H336" t="s">
-        <v>292</v>
+        <v>241</v>
       </c>
       <c r="I336"/>
       <c r="J336"/>
@@ -7808,7 +7583,7 @@
         <v>45657</v>
       </c>
       <c r="B337" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C337"/>
       <c r="D337"/>
@@ -7816,7 +7591,7 @@
       <c r="F337"/>
       <c r="G337"/>
       <c r="H337" t="s">
-        <v>293</v>
+        <v>242</v>
       </c>
       <c r="I337"/>
       <c r="J337"/>
@@ -7827,7 +7602,7 @@
         <v>45688</v>
       </c>
       <c r="B338" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C338"/>
       <c r="D338"/>
@@ -7835,7 +7610,7 @@
       <c r="F338"/>
       <c r="G338"/>
       <c r="H338" t="s">
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="I338"/>
       <c r="J338"/>
@@ -7854,7 +7629,7 @@
       <c r="F339"/>
       <c r="G339"/>
       <c r="H339" t="s">
-        <v>295</v>
+        <v>46</v>
       </c>
       <c r="I339"/>
       <c r="J339"/>
@@ -7873,7 +7648,7 @@
       <c r="F340"/>
       <c r="G340"/>
       <c r="H340" t="s">
-        <v>296</v>
+        <v>244</v>
       </c>
       <c r="I340"/>
       <c r="J340"/>
@@ -7884,7 +7659,7 @@
         <v>45688</v>
       </c>
       <c r="B341" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C341"/>
       <c r="D341"/>
@@ -7892,7 +7667,7 @@
       <c r="F341"/>
       <c r="G341"/>
       <c r="H341" t="s">
-        <v>297</v>
+        <v>240</v>
       </c>
       <c r="I341"/>
       <c r="J341"/>
@@ -7903,7 +7678,7 @@
         <v>45716</v>
       </c>
       <c r="B342" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C342"/>
       <c r="D342"/>
@@ -7911,7 +7686,7 @@
       <c r="F342"/>
       <c r="G342"/>
       <c r="H342" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="I342"/>
       <c r="J342"/>
@@ -7922,7 +7697,7 @@
         <v>45716</v>
       </c>
       <c r="B343" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C343"/>
       <c r="D343"/>
@@ -7930,7 +7705,7 @@
       <c r="F343"/>
       <c r="G343"/>
       <c r="H343" t="s">
-        <v>299</v>
+        <v>195</v>
       </c>
       <c r="I343"/>
       <c r="J343"/>
@@ -7941,7 +7716,7 @@
         <v>45716</v>
       </c>
       <c r="B344" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C344"/>
       <c r="D344"/>
@@ -7949,7 +7724,7 @@
       <c r="F344"/>
       <c r="G344"/>
       <c r="H344" t="s">
-        <v>300</v>
+        <v>49</v>
       </c>
       <c r="I344"/>
       <c r="J344"/>
@@ -7960,7 +7735,7 @@
         <v>45716</v>
       </c>
       <c r="B345" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C345"/>
       <c r="D345"/>
@@ -7968,7 +7743,7 @@
       <c r="F345"/>
       <c r="G345"/>
       <c r="H345" t="s">
-        <v>301</v>
+        <v>64</v>
       </c>
       <c r="I345"/>
       <c r="J345"/>
@@ -7979,7 +7754,7 @@
         <v>45747</v>
       </c>
       <c r="B346" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C346"/>
       <c r="D346"/>
@@ -7987,7 +7762,7 @@
       <c r="F346"/>
       <c r="G346"/>
       <c r="H346" t="s">
-        <v>302</v>
+        <v>47</v>
       </c>
       <c r="I346"/>
       <c r="J346"/>
@@ -7998,7 +7773,7 @@
         <v>45747</v>
       </c>
       <c r="B347" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C347"/>
       <c r="D347"/>
@@ -8006,7 +7781,7 @@
       <c r="F347"/>
       <c r="G347"/>
       <c r="H347" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I347"/>
       <c r="J347"/>
@@ -8017,7 +7792,7 @@
         <v>45747</v>
       </c>
       <c r="B348" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C348"/>
       <c r="D348"/>
@@ -8025,7 +7800,7 @@
       <c r="F348"/>
       <c r="G348"/>
       <c r="H348" t="s">
-        <v>303</v>
+        <v>143</v>
       </c>
       <c r="I348"/>
       <c r="J348"/>
@@ -8044,7 +7819,7 @@
       <c r="F349"/>
       <c r="G349"/>
       <c r="H349" t="s">
-        <v>304</v>
+        <v>42</v>
       </c>
       <c r="I349"/>
       <c r="J349"/>
@@ -8063,7 +7838,7 @@
       <c r="F350"/>
       <c r="G350"/>
       <c r="H350" t="s">
-        <v>305</v>
+        <v>52</v>
       </c>
       <c r="I350"/>
       <c r="J350"/>
@@ -8082,7 +7857,7 @@
       <c r="F351"/>
       <c r="G351"/>
       <c r="H351" t="s">
-        <v>306</v>
+        <v>246</v>
       </c>
       <c r="I351"/>
       <c r="J351"/>
@@ -8093,7 +7868,7 @@
         <v>45777</v>
       </c>
       <c r="B352" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C352"/>
       <c r="D352"/>
@@ -8101,7 +7876,7 @@
       <c r="F352"/>
       <c r="G352"/>
       <c r="H352" t="s">
-        <v>307</v>
+        <v>14</v>
       </c>
       <c r="I352"/>
       <c r="J352"/>
@@ -8112,7 +7887,7 @@
         <v>45777</v>
       </c>
       <c r="B353" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C353"/>
       <c r="D353"/>
@@ -8120,7 +7895,7 @@
       <c r="F353"/>
       <c r="G353"/>
       <c r="H353" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="I353"/>
       <c r="J353"/>
@@ -8131,7 +7906,7 @@
         <v>45808</v>
       </c>
       <c r="B354" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C354"/>
       <c r="D354"/>
@@ -8139,7 +7914,7 @@
       <c r="F354"/>
       <c r="G354"/>
       <c r="H354" t="s">
-        <v>308</v>
+        <v>247</v>
       </c>
       <c r="I354"/>
       <c r="J354"/>
@@ -8150,7 +7925,7 @@
         <v>45808</v>
       </c>
       <c r="B355" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C355"/>
       <c r="D355"/>
@@ -8158,7 +7933,7 @@
       <c r="F355"/>
       <c r="G355"/>
       <c r="H355" t="s">
-        <v>309</v>
+        <v>248</v>
       </c>
       <c r="I355"/>
       <c r="J355"/>
@@ -8169,7 +7944,7 @@
         <v>45808</v>
       </c>
       <c r="B356" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C356"/>
       <c r="D356"/>
@@ -8177,7 +7952,7 @@
       <c r="F356"/>
       <c r="G356"/>
       <c r="H356" t="s">
-        <v>310</v>
+        <v>249</v>
       </c>
       <c r="I356"/>
       <c r="J356"/>
@@ -8196,7 +7971,7 @@
       <c r="F357"/>
       <c r="G357"/>
       <c r="H357" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="I357"/>
       <c r="J357"/>
@@ -8207,7 +7982,7 @@
         <v>45838</v>
       </c>
       <c r="B358" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C358"/>
       <c r="D358"/>
@@ -8215,7 +7990,7 @@
       <c r="F358"/>
       <c r="G358"/>
       <c r="H358" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="I358"/>
       <c r="J358"/>
@@ -8226,7 +8001,7 @@
         <v>45838</v>
       </c>
       <c r="B359" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C359"/>
       <c r="D359"/>
@@ -8234,7 +8009,7 @@
       <c r="F359"/>
       <c r="G359"/>
       <c r="H359" t="s">
-        <v>311</v>
+        <v>250</v>
       </c>
       <c r="I359"/>
       <c r="J359"/>
@@ -8245,7 +8020,7 @@
         <v>45838</v>
       </c>
       <c r="B360" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C360"/>
       <c r="D360"/>
@@ -8253,7 +8028,7 @@
       <c r="F360"/>
       <c r="G360"/>
       <c r="H360" t="s">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="I360"/>
       <c r="J360"/>
@@ -8264,7 +8039,7 @@
         <v>45838</v>
       </c>
       <c r="B361" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C361"/>
       <c r="D361"/>
@@ -8272,7 +8047,7 @@
       <c r="F361"/>
       <c r="G361"/>
       <c r="H361" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="I361"/>
       <c r="J361"/>
@@ -8283,7 +8058,7 @@
         <v>45869</v>
       </c>
       <c r="B362" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C362"/>
       <c r="D362"/>
@@ -8291,7 +8066,7 @@
       <c r="F362"/>
       <c r="G362"/>
       <c r="H362" t="s">
-        <v>313</v>
+        <v>45</v>
       </c>
       <c r="I362"/>
       <c r="J362"/>
@@ -8302,7 +8077,7 @@
         <v>45869</v>
       </c>
       <c r="B363" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C363"/>
       <c r="D363"/>
@@ -8310,7 +8085,7 @@
       <c r="F363"/>
       <c r="G363"/>
       <c r="H363" t="s">
-        <v>314</v>
+        <v>251</v>
       </c>
       <c r="I363"/>
       <c r="J363"/>
@@ -8321,7 +8096,7 @@
         <v>45869</v>
       </c>
       <c r="B364" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C364"/>
       <c r="D364"/>
@@ -8329,7 +8104,7 @@
       <c r="F364"/>
       <c r="G364"/>
       <c r="H364" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="I364"/>
       <c r="J364"/>
@@ -8340,7 +8115,7 @@
         <v>45869</v>
       </c>
       <c r="B365" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C365"/>
       <c r="D365"/>
@@ -8348,7 +8123,7 @@
       <c r="F365"/>
       <c r="G365"/>
       <c r="H365" t="s">
-        <v>315</v>
+        <v>165</v>
       </c>
       <c r="I365"/>
       <c r="J365"/>
@@ -8359,7 +8134,7 @@
         <v>45900</v>
       </c>
       <c r="B366" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C366"/>
       <c r="D366"/>
@@ -8367,7 +8142,7 @@
       <c r="F366"/>
       <c r="G366"/>
       <c r="H366" t="s">
-        <v>316</v>
+        <v>252</v>
       </c>
       <c r="I366"/>
       <c r="J366"/>
@@ -8378,7 +8153,7 @@
         <v>45900</v>
       </c>
       <c r="B367" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C367"/>
       <c r="D367"/>
@@ -8386,7 +8161,7 @@
       <c r="F367"/>
       <c r="G367"/>
       <c r="H367" t="s">
-        <v>317</v>
+        <v>56</v>
       </c>
       <c r="I367"/>
       <c r="J367"/>
@@ -8397,7 +8172,7 @@
         <v>45900</v>
       </c>
       <c r="B368" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C368"/>
       <c r="D368"/>
@@ -8405,7 +8180,7 @@
       <c r="F368"/>
       <c r="G368"/>
       <c r="H368" t="s">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="I368"/>
       <c r="J368"/>
@@ -8416,7 +8191,7 @@
         <v>45900</v>
       </c>
       <c r="B369" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C369"/>
       <c r="D369"/>
@@ -8424,7 +8199,7 @@
       <c r="F369"/>
       <c r="G369"/>
       <c r="H369" t="s">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="I369"/>
       <c r="J369"/>
@@ -8435,7 +8210,7 @@
         <v>45930</v>
       </c>
       <c r="B370" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C370"/>
       <c r="D370"/>
@@ -8443,7 +8218,7 @@
       <c r="F370"/>
       <c r="G370"/>
       <c r="H370" t="s">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="I370"/>
       <c r="J370"/>
@@ -8454,7 +8229,7 @@
         <v>45930</v>
       </c>
       <c r="B371" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C371"/>
       <c r="D371"/>
@@ -8462,7 +8237,7 @@
       <c r="F371"/>
       <c r="G371"/>
       <c r="H371" t="s">
-        <v>320</v>
+        <v>254</v>
       </c>
       <c r="I371"/>
       <c r="J371"/>
@@ -8473,7 +8248,7 @@
         <v>45930</v>
       </c>
       <c r="B372" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C372"/>
       <c r="D372"/>
@@ -8481,7 +8256,7 @@
       <c r="F372"/>
       <c r="G372"/>
       <c r="H372" t="s">
-        <v>321</v>
+        <v>255</v>
       </c>
       <c r="I372"/>
       <c r="J372"/>
@@ -8492,7 +8267,7 @@
         <v>45930</v>
       </c>
       <c r="B373" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C373"/>
       <c r="D373"/>
@@ -8500,7 +8275,7 @@
       <c r="F373"/>
       <c r="G373"/>
       <c r="H373" t="s">
-        <v>34</v>
+        <v>256</v>
       </c>
       <c r="I373"/>
       <c r="J373"/>
@@ -8511,7 +8286,7 @@
         <v>45961</v>
       </c>
       <c r="B374" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C374"/>
       <c r="D374"/>
@@ -8519,7 +8294,7 @@
       <c r="F374"/>
       <c r="G374"/>
       <c r="H374" t="s">
-        <v>294</v>
+        <v>218</v>
       </c>
       <c r="I374"/>
       <c r="J374"/>
@@ -8530,7 +8305,7 @@
         <v>45961</v>
       </c>
       <c r="B375" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C375"/>
       <c r="D375"/>
@@ -8538,7 +8313,7 @@
       <c r="F375"/>
       <c r="G375"/>
       <c r="H375" t="s">
-        <v>322</v>
+        <v>257</v>
       </c>
       <c r="I375"/>
       <c r="J375"/>
@@ -8549,7 +8324,7 @@
         <v>45961</v>
       </c>
       <c r="B376" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C376"/>
       <c r="D376"/>
@@ -8557,7 +8332,7 @@
       <c r="F376"/>
       <c r="G376"/>
       <c r="H376" t="s">
-        <v>323</v>
+        <v>166</v>
       </c>
       <c r="I376"/>
       <c r="J376"/>
@@ -8568,7 +8343,7 @@
         <v>45961</v>
       </c>
       <c r="B377" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C377"/>
       <c r="D377"/>
@@ -8576,7 +8351,7 @@
       <c r="F377"/>
       <c r="G377"/>
       <c r="H377" t="s">
-        <v>324</v>
+        <v>107</v>
       </c>
       <c r="I377"/>
       <c r="J377"/>
@@ -8587,7 +8362,7 @@
         <v>45991</v>
       </c>
       <c r="B378" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C378"/>
       <c r="D378"/>
@@ -8595,7 +8370,7 @@
       <c r="F378"/>
       <c r="G378"/>
       <c r="H378" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="I378"/>
       <c r="J378"/>
@@ -8606,7 +8381,7 @@
         <v>45991</v>
       </c>
       <c r="B379" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C379"/>
       <c r="D379"/>
@@ -8614,7 +8389,7 @@
       <c r="F379"/>
       <c r="G379"/>
       <c r="H379" t="s">
-        <v>325</v>
+        <v>258</v>
       </c>
       <c r="I379"/>
       <c r="J379"/>
@@ -8625,7 +8400,7 @@
         <v>45991</v>
       </c>
       <c r="B380" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C380"/>
       <c r="D380"/>
@@ -8633,7 +8408,7 @@
       <c r="F380"/>
       <c r="G380"/>
       <c r="H380" t="s">
-        <v>326</v>
+        <v>259</v>
       </c>
       <c r="I380"/>
       <c r="J380"/>
@@ -8644,7 +8419,7 @@
         <v>45991</v>
       </c>
       <c r="B381" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C381"/>
       <c r="D381"/>
@@ -8652,7 +8427,7 @@
       <c r="F381"/>
       <c r="G381"/>
       <c r="H381" t="s">
-        <v>327</v>
+        <v>166</v>
       </c>
       <c r="I381"/>
       <c r="J381"/>
@@ -8663,7 +8438,7 @@
         <v>46022</v>
       </c>
       <c r="B382" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C382"/>
       <c r="D382"/>
@@ -8671,7 +8446,7 @@
       <c r="F382"/>
       <c r="G382"/>
       <c r="H382" t="s">
-        <v>328</v>
+        <v>35</v>
       </c>
       <c r="I382"/>
       <c r="J382"/>
@@ -8682,7 +8457,7 @@
         <v>46022</v>
       </c>
       <c r="B383" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C383"/>
       <c r="D383"/>
@@ -8690,7 +8465,7 @@
       <c r="F383"/>
       <c r="G383"/>
       <c r="H383" t="s">
-        <v>314</v>
+        <v>108</v>
       </c>
       <c r="I383"/>
       <c r="J383"/>
@@ -8701,7 +8476,7 @@
         <v>46022</v>
       </c>
       <c r="B384" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C384"/>
       <c r="D384"/>
@@ -8709,7 +8484,7 @@
       <c r="F384"/>
       <c r="G384"/>
       <c r="H384" t="s">
-        <v>329</v>
+        <v>260</v>
       </c>
       <c r="I384"/>
       <c r="J384"/>
@@ -8728,7 +8503,7 @@
       <c r="F385"/>
       <c r="G385"/>
       <c r="H385" t="s">
-        <v>285</v>
+        <v>219</v>
       </c>
       <c r="I385"/>
       <c r="J385"/>
@@ -8739,7 +8514,7 @@
         <v>46053</v>
       </c>
       <c r="B386" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C386"/>
       <c r="D386"/>
@@ -8747,7 +8522,7 @@
       <c r="F386"/>
       <c r="G386"/>
       <c r="H386" t="s">
-        <v>330</v>
+        <v>261</v>
       </c>
       <c r="I386"/>
       <c r="J386"/>
@@ -8758,7 +8533,7 @@
         <v>46053</v>
       </c>
       <c r="B387" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C387"/>
       <c r="D387"/>
@@ -8766,7 +8541,7 @@
       <c r="F387"/>
       <c r="G387"/>
       <c r="H387" t="s">
-        <v>331</v>
+        <v>45</v>
       </c>
       <c r="I387"/>
       <c r="J387"/>
@@ -8777,7 +8552,7 @@
         <v>46053</v>
       </c>
       <c r="B388" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C388"/>
       <c r="D388"/>
@@ -8785,7 +8560,7 @@
       <c r="F388"/>
       <c r="G388"/>
       <c r="H388" t="s">
-        <v>301</v>
+        <v>222</v>
       </c>
       <c r="I388"/>
       <c r="J388"/>
@@ -8804,7 +8579,7 @@
       <c r="F389"/>
       <c r="G389"/>
       <c r="H389" t="s">
-        <v>332</v>
+        <v>115</v>
       </c>
       <c r="I389"/>
       <c r="J389"/>
@@ -8815,7 +8590,7 @@
         <v>46081</v>
       </c>
       <c r="B390" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C390"/>
       <c r="D390"/>
@@ -8823,7 +8598,7 @@
       <c r="F390"/>
       <c r="G390"/>
       <c r="H390" t="s">
-        <v>318</v>
+        <v>154</v>
       </c>
       <c r="I390"/>
       <c r="J390"/>
@@ -8834,7 +8609,7 @@
         <v>46081</v>
       </c>
       <c r="B391" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C391"/>
       <c r="D391"/>
@@ -8842,7 +8617,7 @@
       <c r="F391"/>
       <c r="G391"/>
       <c r="H391" t="s">
-        <v>333</v>
+        <v>262</v>
       </c>
       <c r="I391"/>
       <c r="J391"/>
@@ -8853,7 +8628,7 @@
         <v>46081</v>
       </c>
       <c r="B392" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C392"/>
       <c r="D392"/>
@@ -8861,7 +8636,7 @@
       <c r="F392"/>
       <c r="G392"/>
       <c r="H392" t="s">
-        <v>334</v>
+        <v>263</v>
       </c>
       <c r="I392"/>
       <c r="J392"/>
@@ -8872,7 +8647,7 @@
         <v>46081</v>
       </c>
       <c r="B393" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C393"/>
       <c r="D393"/>
@@ -8880,7 +8655,7 @@
       <c r="F393"/>
       <c r="G393"/>
       <c r="H393" t="s">
-        <v>335</v>
+        <v>18</v>
       </c>
       <c r="I393"/>
       <c r="J393"/>
@@ -8891,7 +8666,7 @@
         <v>46112</v>
       </c>
       <c r="B394" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C394"/>
       <c r="D394"/>
@@ -8899,7 +8674,7 @@
       <c r="F394"/>
       <c r="G394"/>
       <c r="H394" t="s">
-        <v>287</v>
+        <v>158</v>
       </c>
       <c r="I394"/>
       <c r="J394"/>
@@ -8910,7 +8685,7 @@
         <v>46112</v>
       </c>
       <c r="B395" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C395"/>
       <c r="D395"/>
@@ -8918,7 +8693,7 @@
       <c r="F395"/>
       <c r="G395"/>
       <c r="H395" t="s">
-        <v>257</v>
+        <v>68</v>
       </c>
       <c r="I395"/>
       <c r="J395"/>
@@ -8929,7 +8704,7 @@
         <v>46112</v>
       </c>
       <c r="B396" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C396"/>
       <c r="D396"/>
@@ -8937,7 +8712,7 @@
       <c r="F396"/>
       <c r="G396"/>
       <c r="H396" t="s">
-        <v>336</v>
+        <v>264</v>
       </c>
       <c r="I396"/>
       <c r="J396"/>
@@ -8948,7 +8723,7 @@
         <v>46112</v>
       </c>
       <c r="B397" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C397"/>
       <c r="D397"/>
@@ -8956,7 +8731,7 @@
       <c r="F397"/>
       <c r="G397"/>
       <c r="H397" t="s">
-        <v>337</v>
+        <v>192</v>
       </c>
       <c r="I397"/>
       <c r="J397"/>
@@ -8967,7 +8742,7 @@
         <v>46142</v>
       </c>
       <c r="B398" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C398"/>
       <c r="D398"/>
@@ -8975,7 +8750,7 @@
       <c r="F398"/>
       <c r="G398"/>
       <c r="H398" t="s">
-        <v>62</v>
+        <v>265</v>
       </c>
       <c r="I398"/>
       <c r="J398"/>
@@ -8986,7 +8761,7 @@
         <v>46142</v>
       </c>
       <c r="B399" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C399"/>
       <c r="D399"/>
@@ -8994,7 +8769,7 @@
       <c r="F399"/>
       <c r="G399"/>
       <c r="H399" t="s">
-        <v>338</v>
+        <v>74</v>
       </c>
       <c r="I399"/>
       <c r="J399"/>
@@ -9005,7 +8780,7 @@
         <v>46142</v>
       </c>
       <c r="B400" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C400"/>
       <c r="D400"/>
@@ -9013,7 +8788,7 @@
       <c r="F400"/>
       <c r="G400"/>
       <c r="H400" t="s">
-        <v>339</v>
+        <v>66</v>
       </c>
       <c r="I400"/>
       <c r="J400"/>
@@ -9024,7 +8799,7 @@
         <v>46142</v>
       </c>
       <c r="B401" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C401"/>
       <c r="D401"/>
@@ -9032,7 +8807,7 @@
       <c r="F401"/>
       <c r="G401"/>
       <c r="H401" t="s">
-        <v>340</v>
+        <v>174</v>
       </c>
       <c r="I401"/>
       <c r="J401"/>
